--- a/clean/provincial_listings_2026-10-15.xlsx
+++ b/clean/provincial_listings_2026-10-15.xlsx
@@ -58,8 +58,8 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -536,15 +536,12 @@
           <t>国际商学院</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>45996</v>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>北京外国语大学2026年教学科研岗位招聘公告</t>
         </is>
@@ -559,7 +556,7 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>https://www.bfsu.edu.cn/info/1062/23822.htm</t>
         </is>
@@ -596,15 +593,12 @@
           <t>国际商学院</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
-        <v>46136</v>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>北京外国语大学2026年第二批教学科研岗位招聘公告</t>
         </is>
@@ -619,7 +613,7 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>https://www.bfsu.edu.cn/info/1062/26262.htm</t>
         </is>
@@ -662,7 +656,7 @@
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>【诚聘英才】北京理工大学经济学院专任教师及博士后招聘公告</t>
         </is>
@@ -677,7 +671,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>https://soe.bit.edu.cn/lbt/b2d5331b505c49a3bc98591c4b90f43f.htm</t>
         </is>
@@ -725,7 +719,7 @@
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>北京交通大学经济管理学院教师岗位招聘启事（常年有效）</t>
         </is>
@@ -740,7 +734,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>https://jingguan.bjtu.edu.cn/show-972-9001.html</t>
         </is>
@@ -777,12 +771,15 @@
           <t>经济与管理学院</t>
         </is>
       </c>
+      <c r="F6" s="3" t="n">
+        <v>46341</v>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>北京工业大学2026年公开招聘公告（第二批）</t>
         </is>
@@ -797,7 +794,7 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>https://www.bjut.edu.cn/info/1072/9464.htm</t>
         </is>
@@ -839,7 +836,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>北京航空航天大学经济管理学院2026年卓越百人博士后岗位招聘通知</t>
         </is>
@@ -854,7 +851,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>http://boshihouzp.gaoxiaozp.com/gxbshzp/57840.html</t>
         </is>
@@ -897,7 +894,7 @@
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>北航经管学院诚邀海内外优秀学者加盟！</t>
         </is>
@@ -912,7 +909,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>https://sem.buaa.edu.cn/info/1024/16832.htm</t>
         </is>
@@ -959,7 +956,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>北京师范大学经济与工商管理学院2026年招收博士后公告</t>
         </is>
@@ -974,7 +971,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>http://boshihoujob.com/gxbsh/beijing/133313.html</t>
         </is>
@@ -1016,7 +1013,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>北京师范大学经济与工商管理学院2026年招收博士后公告（全球人才网）</t>
         </is>
@@ -1031,7 +1028,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>https://ifegg.com/html/12654.html</t>
         </is>
@@ -1073,7 +1070,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>北京师范大学经济与工商管理学院教学科研岗招聘启事（2026年）</t>
         </is>
@@ -1088,7 +1085,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>https://bs.bnu.edu.cn/bshzs/e8dc0779c4714d7b937e7a7634f44d20.html</t>
         </is>
@@ -1135,7 +1132,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>北师大经管学院教学科研岗位人才招聘启事（2026年）</t>
         </is>
@@ -1150,7 +1147,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>https://www.efnchina.com/info/1111/59261.htm</t>
         </is>
@@ -1192,32 +1189,34 @@
           <t>经济管理学院</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>46091</v>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>中国农业大学2026年度人才招聘启事</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>【诚聘】中国农业大学经济管理学院诚聘天下英才</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>高层次/普通学术岗全年招聘</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>https://cau.edu.cn/tzgg/7080fc338ac04c4c87c78e37531fef46.htm</t>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>https://cem.cau.edu.cn/art/2025/12/16/art_56853_1127416.html</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2017062@cau.edu.cn</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1254,32 +1253,27 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>【诚聘】中国农业大学经济管理学院诚聘天下英才</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>中国农业大学2026年度人才招聘启事</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>高层次/普通学术岗全年招聘</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Dept/HR</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>https://cem.cau.edu.cn/art/2025/12/16/art_56853_1127416.html</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>2017062@cau.edu.cn</t>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>https://cau.edu.cn/tzgg/7080fc338ac04c4c87c78e37531fef46.htm</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1314,15 +1308,12 @@
           <t>经济与管理学院</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n">
-        <v>46185</v>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>中国传媒大学2026年第二批教学科研岗公开招聘公告</t>
         </is>
@@ -1337,7 +1328,7 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>https://mkszyxy.cuc.edu.cn/2026/0603/c2346a271304/page.htm</t>
         </is>
@@ -1370,12 +1361,15 @@
           <t>经济学院</t>
         </is>
       </c>
+      <c r="F16" s="3" t="n">
+        <v>46356</v>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>首都经济贸易大学2026年公开招聘公告</t>
         </is>
@@ -1390,7 +1384,7 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>https://rsj.beijing.gov.cn/xxgk/gkzp/202601/t20260130_4477634.html</t>
         </is>
@@ -1423,12 +1417,15 @@
           <t>经济学院</t>
         </is>
       </c>
+      <c r="F17" s="3" t="n">
+        <v>46356</v>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>首都经济贸易大学2026年公开招聘公告（第二批）</t>
         </is>
@@ -1443,7 +1440,7 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>https://rsj.beijing.gov.cn/xxgk/gkzp/202606/t20260630_4740194.html</t>
         </is>
@@ -1477,35 +1474,35 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>商学院</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>45991</v>
+          <t>经济学院/商学院</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>46326</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>中央财经大学商学院2026年度教学科研岗招聘公告</t>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>中央财经大学2026年度教学科研相关岗位人才招聘公告（第一批）</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>含师资博士后通道</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Dept/HR</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>https://bs.cufe.edu.cn/info/1019/10469.htm</t>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>https://hr.cufe.edu.cn/info/1046/3431.htm</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1537,20 +1534,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>金融学院</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>46083</v>
+          <t>经济学院/商学院</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>金融学院2026年度博士后研究人员招收简章</t>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>中央财经大学2026年度人才招聘公告（第三批）</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1560,17 +1559,17 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Dept/HR</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>https://sf.cufe.edu.cn/info/1104/15771.htm</t>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cufe.edu.cn/info/1186/26673.htm</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -1600,15 +1599,17 @@
           <t>经济学院/商学院</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n">
-        <v>46085</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>中央财经大学2026年度人才招聘公告（第二批）</t>
         </is>
@@ -1623,7 +1624,7 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>https://www.cufe.edu.cn/info/1186/26420.htm</t>
         </is>
@@ -1660,15 +1661,12 @@
           <t>应用经济学/理论经济学/工商管理</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n">
-        <v>46090</v>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>中央财经大学2026年度第一批博士后研究人员招收简章</t>
         </is>
@@ -1683,7 +1681,7 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>https://postdoctor.cufe.edu.cn/info/1014/1396.htm</t>
         </is>
@@ -1720,15 +1718,12 @@
           <t>应用经济学/理论经济学/工商管理</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n">
-        <v>46090</v>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>中央财经大学2026年度第一批博士后研究人员招收简章（校官网）</t>
         </is>
@@ -1743,7 +1738,7 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>https://www.cufe.edu.cn/info/1186/26475.htm</t>
         </is>
@@ -1777,20 +1772,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>管理科学与工程学院</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>46090</v>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>中央财经大学管理科学与工程学院2026年度第一批龙马博士后研究人员招收简章</t>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>中央财经大学商学院2026年度教学科研岗招聘公告</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1803,14 +1800,14 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>https://mse.cufe.edu.cn/info/1073/12521.htm</t>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>https://bs.cufe.edu.cn/info/1019/10469.htm</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -1837,20 +1834,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>经济学院/商学院</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>46129</v>
+          <t>商学院、科技商学院</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>中央财经大学2026年度人才招聘公告（第三批）</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>中央财经大学商学院、科技商学院2026年度教学科研岗招聘公告（第三批）</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1860,12 +1859,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>https://www.cufe.edu.cn/info/1186/26673.htm</t>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>http://bs.cufe.edu.cn/info/1019/11089.htm</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1897,20 +1896,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>商学院、科技商学院</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>46187</v>
+          <t>管理科学与工程学院</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>中央财经大学商学院、科技商学院2026年度教学科研岗招聘公告（第三批）</t>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>中央财经大学管理科学与工程学院2026年度第一批龙马博士后研究人员招收简章</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1923,14 +1919,14 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>http://bs.cufe.edu.cn/info/1019/11089.htm</t>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>https://mse.cufe.edu.cn/info/1073/12521.htm</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -1957,12 +1953,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>经济学院/商学院</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Rolling</t>
+          <t>金融学院</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1970,29 +1961,29 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>中央财经大学2026年度教学科研相关岗位人才招聘公告（第一批）</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>金融学院2026年度博士后研究人员招收简章</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>含师资博士后通道</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>https://hr.cufe.edu.cn/info/1046/3431.htm</t>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>https://sf.cufe.edu.cn/info/1104/15771.htm</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -2022,15 +2013,12 @@
           <t>经济管理学院</t>
         </is>
       </c>
-      <c r="F27" s="2" t="n">
-        <v>46143</v>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>中国地质大学（北京）2026年教师岗、实验员岗及专技岗位招聘启事（第二批）</t>
         </is>
@@ -2045,7 +2033,7 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>https://bm.cugb.edu.cn/rscnew/c/2026-04-30/849146.shtml</t>
         </is>
@@ -2078,7 +2066,7 @@
           <t>经管学院</t>
         </is>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="F28" s="3" t="n">
         <v>46326</v>
       </c>
       <c r="G28" t="inlineStr">
@@ -2086,7 +2074,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>香港中文大学（深圳）经管学院姜翰项目2026年博士后招聘启事</t>
         </is>
@@ -2101,7 +2089,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/372342.html</t>
         </is>
@@ -2134,7 +2122,7 @@
           <t>经管学院</t>
         </is>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="F29" s="3" t="n">
         <v>46326</v>
       </c>
       <c r="G29" t="inlineStr">
@@ -2142,7 +2130,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>香港中文大学（深圳）经管学院李琦项目2026年博士后招聘启事</t>
         </is>
@@ -2157,7 +2145,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/372343.html</t>
         </is>
@@ -2190,7 +2178,7 @@
           <t>经管学院</t>
         </is>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="F30" s="3" t="n">
         <v>46326</v>
       </c>
       <c r="G30" t="inlineStr">
@@ -2198,7 +2186,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>香港中文大学（深圳）经管学院申睿项目2026年博士后招聘公告</t>
         </is>
@@ -2213,7 +2201,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/371642.html</t>
         </is>
@@ -2255,7 +2243,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>中国矿业大学2026年博士后招聘（含经管学院）</t>
         </is>
@@ -2270,7 +2258,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/383481.html</t>
         </is>
@@ -2312,7 +2300,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>中国矿业大学2026年高层次人才引进</t>
         </is>
@@ -2327,7 +2315,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/356248.html</t>
         </is>
@@ -2365,7 +2353,7 @@
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>中国石油大学（北京）经济管理学院诚聘优秀人才</t>
         </is>
@@ -2380,7 +2368,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>https://www.cup.edu.cn/sba/rczp/a11fe97eb87141269783d3fded8c4456.htm</t>
         </is>
@@ -2427,7 +2415,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>中国石油大学（华东）经济管理学院教师招聘启事</t>
         </is>
@@ -2442,7 +2430,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>https://sem.upc.edu.cn/2025/0402/c19374a454231/page.htm</t>
         </is>
@@ -2484,7 +2472,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>大连海事大学2026年度专任教师（博士）招聘公告</t>
         </is>
@@ -2499,7 +2487,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>https://rcb.dlmu.edu.cn/info/1013/4752.htm</t>
         </is>
@@ -2533,7 +2521,7 @@
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>东北财经大学管理科学与工程学院诚聘英才</t>
         </is>
@@ -2548,7 +2536,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K36" s="3" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>https://smse.dufe.edu.cn/content_98151.html</t>
         </is>
@@ -2582,7 +2570,7 @@
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>东北财经大学经济学院诚聘天下英才</t>
         </is>
@@ -2597,7 +2585,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>https://econ.dufe.edu.cn/content_95758.html</t>
         </is>
@@ -2631,7 +2619,7 @@
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>东北财经大学财政税务学院诚聘海内外英才</t>
         </is>
@@ -2646,7 +2634,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>https://cs.dufe.edu.cn/content_96670.html</t>
         </is>
@@ -2688,7 +2676,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>大连理工大学2026年全球人才招聘</t>
         </is>
@@ -2703,7 +2691,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K39" s="3" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>https://perdep.dlut.edu.cn/info/1401/21541.htm</t>
         </is>
@@ -2745,7 +2733,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>大连理工大学2026年博士后招聘公告</t>
         </is>
@@ -2760,7 +2748,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K40" s="3" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>https://perdep.dlut.edu.cn/info/1401/21561.htm</t>
         </is>
@@ -2802,7 +2790,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>大连理工大学盘锦校区2026年专任教师招聘公告</t>
         </is>
@@ -2817,7 +2805,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K41" s="3" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>https://panjin.dlut.edu.cn/info/1342/48784.htm</t>
         </is>
@@ -2855,7 +2843,7 @@
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>大连理工大学经济管理学院诚聘海内外优秀人才</t>
         </is>
@@ -2870,7 +2858,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K42" s="3" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>http://sem.dlut.edu.cn/info/1072/7620.htm</t>
         </is>
@@ -2917,7 +2905,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>东华大学旭日工商管理学院研究助理教授（RAP）招聘公告</t>
         </is>
@@ -2932,7 +2920,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K43" s="3" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>https://glxy.dhu.edu.cn/2026/0520/c20103a376231/page.htm</t>
         </is>
@@ -2979,7 +2967,7 @@
           <t>2033</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>东华大学旭日工商管理学院诚聘海内外英才</t>
         </is>
@@ -2994,7 +2982,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K44" s="3" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>https://glxy.dhu.edu.cn/2024/1014/c20103a352033/page.htm</t>
         </is>
@@ -3041,7 +3029,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>东华大学旭日工商管理学院诚聘海内外高层次人才</t>
         </is>
@@ -3056,7 +3044,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K45" s="3" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>https://glxy.dhu.edu.cn/2026/0520/c20103a376232/page.htm</t>
         </is>
@@ -3099,7 +3087,7 @@
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>华东师范大学中国自贸战略研究院博士后研究员招聘启事（长期有效）</t>
         </is>
@@ -3114,7 +3102,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>https://sem.ecnu.edu.cn/42/d7/c42845a738007/page.htm</t>
         </is>
@@ -3162,7 +3150,7 @@
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>华东师范大学中国自贸战略研究院招聘启事（长期有效）</t>
         </is>
@@ -3177,7 +3165,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K47" s="3" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>https://sem.ecnu.edu.cn/42/d8/c42845a738008/page.htm</t>
         </is>
@@ -3220,7 +3208,7 @@
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>华东理工大学陈万思教授团队招聘博士后启事</t>
         </is>
@@ -3235,7 +3223,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K48" s="3" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>https://bs.ecust.edu.cn/cms/ecust/szyky/szdw/zpqs.html</t>
         </is>
@@ -3273,7 +3261,7 @@
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>商学院管理科学与工程博士后科研流动站招聘启事</t>
         </is>
@@ -3288,7 +3276,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K49" s="3" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>https://bs.ecust.edu.cn/cms/ecust/facultyAndResearch/teacherRecruit/450106463682564.html</t>
         </is>
@@ -3321,7 +3309,7 @@
           <t>协和学院</t>
         </is>
       </c>
-      <c r="F50" s="2" t="n">
+      <c r="F50" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G50" t="inlineStr">
@@ -3329,7 +3317,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>福建师范大学协和学院2026年高层次人才招聘公告</t>
         </is>
@@ -3344,7 +3332,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K50" s="3" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>https://cuc.fjnu.edu.cn/2026/0518/c315a43167/page.htm</t>
         </is>
@@ -3377,8 +3365,11 @@
           <t>经济学院</t>
         </is>
       </c>
+      <c r="F51" s="3" t="n">
+        <v>46387</v>
+      </c>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>福建师范大学理论经济学【经济学院-教研岗】招聘</t>
         </is>
@@ -3393,7 +3384,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K51" s="3" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>https://www.sciencehr.net/job/227601.html</t>
         </is>
@@ -3426,7 +3417,7 @@
           <t>??????</t>
         </is>
       </c>
-      <c r="F52" s="2" t="n">
+      <c r="F52" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G52" t="inlineStr">
@@ -3434,7 +3425,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>2026年福建江夏学院公开招聘博士高层次人才方案</t>
         </is>
@@ -3449,7 +3440,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K52" s="3" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>https://rst.fujian.gov.cn/zw/ztzl/zxzt/sydwrczp/gccrczpfa/202603/t20260330_7117115.htm</t>
         </is>
@@ -3482,7 +3473,7 @@
           <t>??????</t>
         </is>
       </c>
-      <c r="F53" s="2" t="n">
+      <c r="F53" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G53" t="inlineStr">
@@ -3490,7 +3481,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>福建江夏学院2026年博士高层次人才招聘公告</t>
         </is>
@@ -3505,7 +3496,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K53" s="3" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>https://rsc.fjjxu.edu.cn/2026/0402/c2784a119519/page.htm</t>
         </is>
@@ -3539,7 +3530,7 @@
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>佛山大学数字经济【经济贸易学院-高层次人才】招聘</t>
         </is>
@@ -3554,7 +3545,7 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="K54" s="3" t="inlineStr">
+      <c r="K54" s="2" t="inlineStr">
         <is>
           <t>https://www.sciencehr.net/job/193240.html</t>
         </is>
@@ -3591,7 +3582,7 @@
           <t>经济学院</t>
         </is>
       </c>
-      <c r="F55" s="2" t="n">
+      <c r="F55" s="3" t="n">
         <v>46327</v>
       </c>
       <c r="G55" t="inlineStr">
@@ -3599,7 +3590,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>【2026年】复旦大学经济学院面向全球诚聘英才，热岑欢迎您的加盟</t>
         </is>
@@ -3614,7 +3605,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K55" s="3" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>https://econ.fudan.edu.cn/info/1134/46327.htm</t>
         </is>
@@ -3647,7 +3638,7 @@
           <t>互联网经贸学院</t>
         </is>
       </c>
-      <c r="F56" s="2" t="n">
+      <c r="F56" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G56" t="inlineStr">
@@ -3655,7 +3646,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>福建理工大学2026年高层次人才招聘方案</t>
         </is>
@@ -3670,7 +3661,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K56" s="3" t="inlineStr">
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t>https://rst.fujian.gov.cn/zw/ztzl/zxzt/sydwrczp/gccrczpfa/202603/t20260330_7117134.htm</t>
         </is>
@@ -3689,7 +3680,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>??</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3704,27 +3695,25 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>经济与管理学院</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Rolling</t>
-        </is>
+          <t>???????</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>46387</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>2026年福州大学高层次专业技术人员招聘方案（含经管）</t>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>2026年福州大学高层次教学科研人员招聘方案（含经管学院）</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>招满即止</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3732,9 +3721,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t>https://rsc.fzu.edu.cn/info/1071/2642.htm</t>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>https://rsc.fzu.edu.cn/info/1071/2641.htm</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3751,7 +3740,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>??</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3766,7 +3755,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>???????</t>
+          <t>经济与管理学院</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3779,14 +3768,14 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>2026年福州大学高层次教学科研人员招聘方案（含经管学院）</t>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>2026年福州大学高层次专业技术人员招聘方案（含经管）</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>招满即止</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3794,9 +3783,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t>https://rsc.fzu.edu.cn/info/1071/2641.htm</t>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>https://rsc.fzu.edu.cn/info/1071/2642.htm</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -3832,7 +3821,7 @@
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>常态化招聘！福州大学诚聘师资博士后（含经管学院）</t>
         </is>
@@ -3847,7 +3836,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K59" s="3" t="inlineStr">
+      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>https://rsc.fzu.edu.cn/info/1071/2514.htm</t>
         </is>
@@ -3889,7 +3878,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>欢迎申报2026福州大学经济与管理学院博士后引才项目</t>
         </is>
@@ -3904,7 +3893,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K60" s="3" t="inlineStr">
+      <c r="K60" s="2" t="inlineStr">
         <is>
           <t>https://jgxy.fzu.edu.cn/info/1127/24608.htm</t>
         </is>
@@ -3941,7 +3930,7 @@
           <t>国际商学院</t>
         </is>
       </c>
-      <c r="F61" s="2" t="n">
+      <c r="F61" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G61" t="inlineStr">
@@ -3949,7 +3938,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>福州外语外贸学院2026年优秀博士招聘公告</t>
         </is>
@@ -3964,7 +3953,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K61" s="3" t="inlineStr">
+      <c r="K61" s="2" t="inlineStr">
         <is>
           <t>https://www.fzfu.com/jsfzzx/info/1054/2245.htm</t>
         </is>
@@ -4006,7 +3995,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>福州外语外贸学院2026年高层次人才招聘公告</t>
         </is>
@@ -4021,7 +4010,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K62" s="3" t="inlineStr">
+      <c r="K62" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/198488.html</t>
         </is>
@@ -4059,7 +4048,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>【百万英才汇南粤】广东金融学院2026年大数据与人工智能学院诚聘师资公告</t>
         </is>
@@ -4074,7 +4063,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K63" s="3" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>https://ai.gduf.edu.cn/info/1099/1240.htm</t>
         </is>
@@ -4118,7 +4107,7 @@
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" s="3" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>广东工业大学经济学院高层次人才招聘</t>
         </is>
@@ -4133,7 +4122,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K64" s="3" t="inlineStr">
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>https://jjxy.gdut.edu.cn/info/1055/3235.htm</t>
         </is>
@@ -4172,7 +4161,7 @@
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" s="3" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>百万英才汇南粤--广东工业大学高层次人才招聘简章（经济学院）</t>
         </is>
@@ -4187,7 +4176,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K65" s="3" t="inlineStr">
+      <c r="K65" s="2" t="inlineStr">
         <is>
           <t>https://hr.gdut.edu.cn/info/1073/1195.htm</t>
         </is>
@@ -4225,7 +4214,7 @@
           <t>经济学院</t>
         </is>
       </c>
-      <c r="F66" s="2" t="n">
+      <c r="F66" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G66" t="inlineStr">
@@ -4233,7 +4222,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>广西财经学院2026年招聘高层次人才公告</t>
         </is>
@@ -4248,7 +4237,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K66" s="3" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/409543.html</t>
         </is>
@@ -4286,7 +4275,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>“百万英才汇南粤”广东财经大学2026年博士后招聘公告</t>
         </is>
@@ -4301,7 +4290,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K67" s="3" t="inlineStr">
+      <c r="K67" s="2" t="inlineStr">
         <is>
           <t>http://rsc.gdufe.edu.cn/2026/0306/c4710a233784/page.htm</t>
         </is>
@@ -4339,7 +4328,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>广东财经大学2026年招聘博士后（经济学/管理学/法学等）</t>
         </is>
@@ -4354,7 +4343,7 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="K68" s="3" t="inlineStr">
+      <c r="K68" s="2" t="inlineStr">
         <is>
           <t>http://rsc.gdufe.edu.cn/2026/0429/c4948a238378/page.htm</t>
         </is>
@@ -4397,7 +4386,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>广东财经大学面向海内外招聘学科方向带头人的公告</t>
         </is>
@@ -4412,7 +4401,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K69" s="3" t="inlineStr">
+      <c r="K69" s="2" t="inlineStr">
         <is>
           <t>http://rsc.gdufe.edu.cn/2025/0116/c12800a215856/page.htm</t>
         </is>
@@ -4450,7 +4439,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>广东外语外贸大学2026年招聘师资博士后研究...</t>
         </is>
@@ -4465,7 +4454,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K70" s="3" t="inlineStr">
+      <c r="K70" s="2" t="inlineStr">
         <is>
           <t>https://rsc.gdufs.edu.cn/info/1083/12549.htm</t>
         </is>
@@ -4503,7 +4492,7 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>广东外语外贸大学应用经济学博士后科研流动站2024年科研博士后研究人员招聘简章</t>
         </is>
@@ -4518,7 +4507,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K71" s="3" t="inlineStr">
+      <c r="K71" s="2" t="inlineStr">
         <is>
           <t>https://rsc.gdufs.edu.cn/info/1083/11977.htm</t>
         </is>
@@ -4556,7 +4545,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>广东外语外贸大学应用经济学博士后科研流动站2025年科研博士后研究人员招聘简章</t>
         </is>
@@ -4571,7 +4560,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K72" s="3" t="inlineStr">
+      <c r="K72" s="2" t="inlineStr">
         <is>
           <t>https://rsc.gdufs.edu.cn/info/1083/12041.htm</t>
         </is>
@@ -4609,7 +4598,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>广东外语外贸大学应用经济学博士后科研流动站2026年科研博士后研究人员招聘简章</t>
         </is>
@@ -4624,7 +4613,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K73" s="3" t="inlineStr">
+      <c r="K73" s="2" t="inlineStr">
         <is>
           <t>https://rsc.gdufs.edu.cn/info/1083/12519.htm</t>
         </is>
@@ -4662,7 +4651,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>广外2026年招聘师资博士后（含应用经济学、金融学）</t>
         </is>
@@ -4677,7 +4666,7 @@
           <t>HR/学院</t>
         </is>
       </c>
-      <c r="K74" s="3" t="inlineStr">
+      <c r="K74" s="2" t="inlineStr">
         <is>
           <t>https://rsc.gdufs.edu.cn/info/1017/12559.htm</t>
         </is>
@@ -4715,7 +4704,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>广外2026年面向海内外招聘人才（经贸学院含国贸/产业/数字经济等）</t>
         </is>
@@ -4730,7 +4719,7 @@
           <t>Email/学院</t>
         </is>
       </c>
-      <c r="K75" s="3" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr">
         <is>
           <t>https://rsc.gdufs.edu.cn/info/1017/12399.htm</t>
         </is>
@@ -4768,7 +4757,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>广外应用经济学博士后科研流动站2026年科研博士后招聘简章</t>
         </is>
@@ -4783,7 +4772,7 @@
           <t>HR/导师</t>
         </is>
       </c>
-      <c r="K76" s="3" t="inlineStr">
+      <c r="K76" s="2" t="inlineStr">
         <is>
           <t>https://rsc.gdufs.edu.cn/info/1017/12909.htm</t>
         </is>
@@ -4825,7 +4814,7 @@
           <t>经济学院</t>
         </is>
       </c>
-      <c r="F77" s="2" t="n">
+      <c r="F77" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G77" t="inlineStr">
@@ -4833,7 +4822,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>广西民族大学2026年度公开招聘专任教师公告</t>
         </is>
@@ -4848,7 +4837,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K77" s="3" t="inlineStr">
+      <c r="K77" s="2" t="inlineStr">
         <is>
           <t>https://rsc.gxmzu.edu.cn/info/1296/10555.htm</t>
         </is>
@@ -4885,11 +4874,11 @@
           <t>工商管理学院</t>
         </is>
       </c>
-      <c r="F78" s="2" t="n">
+      <c r="F78" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G78" t="inlineStr"/>
-      <c r="H78" s="3" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>广西大学海内外人才招聘（含工商管理学院）</t>
         </is>
@@ -4904,7 +4893,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K78" s="3" t="inlineStr">
+      <c r="K78" s="2" t="inlineStr">
         <is>
           <t>https://www.gxu.edu.cn/info/1364/34798.htm</t>
         </is>
@@ -4942,7 +4931,7 @@
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
-      <c r="H79" s="3" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>广西大学经济学院诚聘海内外英才公告</t>
         </is>
@@ -4957,7 +4946,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K79" s="3" t="inlineStr">
+      <c r="K79" s="2" t="inlineStr">
         <is>
           <t>https://sef.gxu.edu.cn/info/10836/90824.htm</t>
         </is>
@@ -5000,7 +4989,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>广州大学2026年高层次人才招聘公告</t>
         </is>
@@ -5015,7 +5004,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K80" s="3" t="inlineStr">
+      <c r="K80" s="2" t="inlineStr">
         <is>
           <t>https://rsc.gzhu.edu.cn/info/1016/8191.htm</t>
         </is>
@@ -5053,7 +5042,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>广州大学经济与统计学院（李正辉课题组）2026年诚聘博士后</t>
         </is>
@@ -5068,7 +5057,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K81" s="3" t="inlineStr">
+      <c r="K81" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/388060.html</t>
         </is>
@@ -5106,7 +5095,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>广州大学经济与统计学院（李正辉课题组）2026年诚聘博士后</t>
         </is>
@@ -5121,7 +5110,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K82" s="3" t="inlineStr">
+      <c r="K82" s="2" t="inlineStr">
         <is>
           <t>https://www.gxszw.com/region/guangdong/gxzpgd/202603/30124547.html</t>
         </is>
@@ -5164,7 +5153,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>百万英才汇南粤 广州大学2026年博士后招聘简章</t>
         </is>
@@ -5179,7 +5168,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K83" s="3" t="inlineStr">
+      <c r="K83" s="2" t="inlineStr">
         <is>
           <t>https://www.gzhu.edu.cn/info/1205/31377.htm</t>
         </is>
@@ -5222,7 +5211,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>广州中医药大学2025-2026学年度学科博士后招收公告</t>
         </is>
@@ -5237,7 +5226,7 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="K84" s="3" t="inlineStr">
+      <c r="K84" s="2" t="inlineStr">
         <is>
           <t>https://www.gzucm.edu.cn/info/1461/114061.htm</t>
         </is>
@@ -5271,7 +5260,7 @@
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
-      <c r="H85" s="3" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>广州中医药大学诚聘海内外英才（含经济与管理类）</t>
         </is>
@@ -5286,7 +5275,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K85" s="3" t="inlineStr">
+      <c r="K85" s="2" t="inlineStr">
         <is>
           <t>https://rsc.gzucm.edu.cn/info/1003/4003.htm</t>
         </is>
@@ -5324,7 +5313,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>杭州电子科技大学2026年博士后招聘启事</t>
         </is>
@@ -5339,7 +5328,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K86" s="3" t="inlineStr">
+      <c r="K86" s="2" t="inlineStr">
         <is>
           <t>https://renshi.hdu.edu.cn/2026/0518/c13760a295531/page.htm</t>
         </is>
@@ -5377,7 +5366,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>杭州电子科技大学2026年诚聘海内外优秀人才</t>
         </is>
@@ -5392,7 +5381,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K87" s="3" t="inlineStr">
+      <c r="K87" s="2" t="inlineStr">
         <is>
           <t>https://m.gaoxiaojob.com/announcement/detail/385225.html</t>
         </is>
@@ -5430,7 +5419,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>杭州电子科技大学2026年诚聘海内外优秀人才</t>
         </is>
@@ -5445,7 +5434,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K88" s="3" t="inlineStr">
+      <c r="K88" s="2" t="inlineStr">
         <is>
           <t>https://renshi.hdu.edu.cn/2026/0313/c13762a290223/page.htm</t>
         </is>
@@ -5483,7 +5472,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>杭州电子科技大学会计学院诚聘海内外优秀人才</t>
         </is>
@@ -5498,7 +5487,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K89" s="3" t="inlineStr">
+      <c r="K89" s="2" t="inlineStr">
         <is>
           <t>https://acc.hdu.edu.cn/2026/0702/c12448a298474/page.htm</t>
         </is>
@@ -5536,7 +5525,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>杭州电子科技大学公开招聘人员公告（2026年第二批）</t>
         </is>
@@ -5551,7 +5540,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K90" s="3" t="inlineStr">
+      <c r="K90" s="2" t="inlineStr">
         <is>
           <t>https://renshi.hdu.edu.cn/2026/0408/c13762a291030/page.htm</t>
         </is>
@@ -5593,7 +5582,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H91" s="3" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>河北工业大学2026年公开选聘工作人员公告（专任教师）</t>
         </is>
@@ -5608,7 +5597,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K91" s="3" t="inlineStr">
+      <c r="K91" s="2" t="inlineStr">
         <is>
           <t>https://www.hebut.edu.cn/rczp/zpgg/be54ac68d1e34c1ab0f57e8afdfc9c8f.htm</t>
         </is>
@@ -5650,7 +5639,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>教师岗位招聘（内含申请材料）</t>
         </is>
@@ -5665,7 +5654,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K92" s="3" t="inlineStr">
+      <c r="K92" s="2" t="inlineStr">
         <is>
           <t>https://www.hitsz.edu.cn/2025/1125/c81a15941/page.htm</t>
         </is>
@@ -5703,7 +5692,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>河北经贸大学2026年公开选聘工作人员公告（第一批）</t>
         </is>
@@ -5718,7 +5707,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K93" s="3" t="inlineStr">
+      <c r="K93" s="2" t="inlineStr">
         <is>
           <t>https://rsc.hueb.edu.cn/info/1068/4413.htm</t>
         </is>
@@ -5751,15 +5740,12 @@
           <t>人事处</t>
         </is>
       </c>
-      <c r="F94" s="2" t="n">
-        <v>46240</v>
-      </c>
       <c r="G94" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>海南师范大学2026年公开招聘专任教师公告</t>
         </is>
@@ -5774,7 +5760,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K94" s="3" t="inlineStr">
+      <c r="K94" s="2" t="inlineStr">
         <is>
           <t>https://www.hainnu.edu.cn/2026/0803/c499a168635/page.htm</t>
         </is>
@@ -5817,7 +5803,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H95" s="3" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>海南师范大学经济与管理学院2026年高层次人才招聘启事</t>
         </is>
@@ -5832,7 +5818,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K95" s="3" t="inlineStr">
+      <c r="K95" s="2" t="inlineStr">
         <is>
           <t>https://jgxy.hainnu.edu.cn/2026/1014/c352a170265/page.htm</t>
         </is>
@@ -5866,13 +5852,20 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>经济学科</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>拥抱自贸港，拥有未来｜海南大学经济学科诚聘海内外高层次人才</t>
+          <t>国际商学院</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>46387</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>海南大学2026年招聘教学科研专业技术人员公告</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5885,14 +5878,14 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K96" s="3" t="inlineStr">
-        <is>
-          <t>http://www.efnchina.com/info/1111/59241.htm</t>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>https://hro.hainanu.edu.cn/info/1009/9413.htm</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -5922,14 +5915,17 @@
           <t>国际商学院</t>
         </is>
       </c>
+      <c r="F97" s="3" t="n">
+        <v>46387</v>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>海南大学2026年全职博士后招收公告</t>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>海南大学2026年招聘教学科研专业技术人员公告（副本）</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5942,9 +5938,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K97" s="3" t="inlineStr">
-        <is>
-          <t>https://hro.hainanu.edu.cn/info/1223/9743.htm</t>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>https://hro.hainanu.edu.cn/info/1074/9473.htm</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -5976,17 +5972,13 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>国际商学院</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>海南大学2026年招聘教学科研专业技术人员公告</t>
+          <t>经济学科</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>拥抱自贸港，拥有未来｜海南大学经济学科诚聘海内外高层次人才</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5999,14 +5991,14 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K98" s="3" t="inlineStr">
-        <is>
-          <t>https://hro.hainanu.edu.cn/info/1009/9413.htm</t>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>http://www.efnchina.com/info/1111/59241.htm</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -6041,9 +6033,9 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>海南大学2026年招聘教学科研专业技术人员公告（副本）</t>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>海南大学2026年全职博士后招收公告</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6056,9 +6048,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K99" s="3" t="inlineStr">
-        <is>
-          <t>https://hro.hainanu.edu.cn/info/1074/9473.htm</t>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>https://hro.hainanu.edu.cn/info/1223/9743.htm</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -6098,7 +6090,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>海南大学诚邀全球英才依托申报2026年海外优青项目</t>
         </is>
@@ -6113,7 +6105,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K100" s="3" t="inlineStr">
+      <c r="K100" s="2" t="inlineStr">
         <is>
           <t>https://hro.hainanu.edu.cn/info/1074/9483.htm</t>
         </is>
@@ -6151,7 +6143,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>河北金融学院2026年公开选聘工作人员公告</t>
         </is>
@@ -6166,7 +6158,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K101" s="3" t="inlineStr">
+      <c r="K101" s="2" t="inlineStr">
         <is>
           <t>https://www.boshijob.com/article/202606/24284866.html</t>
         </is>
@@ -6196,16 +6188,17 @@
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>经济学院</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>45873</v>
-      </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>河北大学经济学院相关招聘</t>
+          <t>人事处</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>河北大学2026年公开选聘工作人员公告</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6218,9 +6211,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K102" s="3" t="inlineStr">
-        <is>
-          <t>https://ec.hbu.edu.cn/info/1084/1669.htm</t>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>https://rsc.hbu.cn/info/1017/2038.htm</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -6248,17 +6241,13 @@
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>人事处</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>河北大学2026年公开选聘工作人员公告</t>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>河北大学经济学院相关招聘</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6271,9 +6260,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K103" s="3" t="inlineStr">
-        <is>
-          <t>https://rsc.hbu.cn/info/1017/2038.htm</t>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>https://ec.hbu.edu.cn/info/1084/1669.htm</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -6309,7 +6298,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>华侨大学2026年邀请海外优秀青年人才开展交流合作的公告</t>
         </is>
@@ -6324,7 +6313,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K104" s="3" t="inlineStr">
+      <c r="K104" s="2" t="inlineStr">
         <is>
           <t>https://jobs.hqu.edu.cn/info/1011/8135.htm</t>
         </is>
@@ -6366,7 +6355,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H105" s="3" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>江南大学2026年人才招聘公告</t>
         </is>
@@ -6381,7 +6370,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K105" s="3" t="inlineStr">
+      <c r="K105" s="2" t="inlineStr">
         <is>
           <t>http://renshi.jiangnan.edu.cn/info/1008/3329.htm</t>
         </is>
@@ -6423,7 +6412,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>江南大学2026年人才招聘公告（新闻网）</t>
         </is>
@@ -6438,7 +6427,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K106" s="3" t="inlineStr">
+      <c r="K106" s="2" t="inlineStr">
         <is>
           <t>https://news.jiangnan.edu.cn/info/1132/106209.htm</t>
         </is>
@@ -6471,17 +6460,17 @@
           <t>财经学院</t>
         </is>
       </c>
-      <c r="F107" s="2" t="n">
-        <v>46133</v>
+      <c r="F107" s="3" t="n">
+        <v>46385</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t>江苏大学2026年公开招聘专任教师公告</t>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>江苏大学2026年公开招聘专任教师公告（高校人才网）</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6494,9 +6483,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K107" s="3" t="inlineStr">
-        <is>
-          <t>https://www.ujs.edu.cn/info/1093/211052.htm</t>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>https://m.gaoxiaojob.com/announcement/detail/395509.html</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -6527,17 +6516,14 @@
           <t>财经学院</t>
         </is>
       </c>
-      <c r="F108" s="2" t="n">
-        <v>46385</v>
-      </c>
       <c r="G108" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>江苏大学2026年公开招聘专任教师公告（高校人才网）</t>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>江苏大学2026年公开招聘专任教师公告</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6550,9 +6536,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K108" s="3" t="inlineStr">
-        <is>
-          <t>https://m.gaoxiaojob.com/announcement/detail/395509.html</t>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ujs.edu.cn/info/1093/211052.htm</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -6583,15 +6569,15 @@
           <t>????</t>
         </is>
       </c>
-      <c r="F109" s="2" t="n">
-        <v>46078</v>
+      <c r="F109" s="3" t="n">
+        <v>46387</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H109" s="3" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>2026年集美大学公开招聘高层次人才方案（含财经）</t>
         </is>
@@ -6606,7 +6592,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K109" s="3" t="inlineStr">
+      <c r="K109" s="2" t="inlineStr">
         <is>
           <t>https://rst.fj.gov.cn/zw/ztzl/zxzt/sydwrczp/gccrczpfa/202602/t20260225_7100631.htm</t>
         </is>
@@ -6639,8 +6625,11 @@
           <t>????</t>
         </is>
       </c>
+      <c r="F110" s="3" t="n">
+        <v>46387</v>
+      </c>
       <c r="G110" t="inlineStr"/>
-      <c r="H110" s="3" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>集美大学经济贸易类（财经学院-高层次人才）招聘</t>
         </is>
@@ -6655,7 +6644,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K110" s="3" t="inlineStr">
+      <c r="K110" s="2" t="inlineStr">
         <is>
           <t>https://www.sciencehr.net/job/211533.html</t>
         </is>
@@ -6697,7 +6686,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H111" s="3" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Job Openings IESR 2026</t>
         </is>
@@ -6712,7 +6701,7 @@
           <t>AEA/Email</t>
         </is>
       </c>
-      <c r="K111" s="3" t="inlineStr">
+      <c r="K111" s="2" t="inlineStr">
         <is>
           <t>https://iesr.jnu.edu.cn/2025/1021/c17720a844641/page.htm</t>
         </is>
@@ -6759,7 +6748,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>招聘通知｜暨南大学经济学院2025年诚聘海内外英才</t>
         </is>
@@ -6774,7 +6763,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K112" s="3" t="inlineStr">
+      <c r="K112" s="2" t="inlineStr">
         <is>
           <t>https://ec.jnu.edu.cn/2024/1129/c24919a826585/page.htm</t>
         </is>
@@ -6821,7 +6810,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H113" s="3" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>暨南大学2026年博士后全球招聘公告</t>
         </is>
@@ -6836,7 +6825,7 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="K113" s="3" t="inlineStr">
+      <c r="K113" s="2" t="inlineStr">
         <is>
           <t>https://hrdam.jnu.edu.cn/2026/0413/c264a853500/page.htm</t>
         </is>
@@ -6878,7 +6867,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H114" s="3" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>暨南大学2026年博士后全球招聘（含应用经济学、理论经济学）</t>
         </is>
@@ -6893,7 +6882,7 @@
           <t>HR/导师</t>
         </is>
       </c>
-      <c r="K114" s="3" t="inlineStr">
+      <c r="K114" s="2" t="inlineStr">
         <is>
           <t>https://hrdam.jnu.edu.cn/2026/0413/c343a853500/page.htm</t>
         </is>
@@ -6935,7 +6924,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H115" s="3" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>暨南大学冯帅章教授团队招聘博士后</t>
         </is>
@@ -6950,7 +6939,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K115" s="3" t="inlineStr">
+      <c r="K115" s="2" t="inlineStr">
         <is>
           <t>https://iesr.jnu.edu.cn/2025/0624/c17209a839104/page.htm</t>
         </is>
@@ -6997,7 +6986,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H116" s="3" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>暨南大学经济学院2025年诚聘海内外英才（含教师各层次与博士后）</t>
         </is>
@@ -7012,7 +7001,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K116" s="3" t="inlineStr">
+      <c r="K116" s="2" t="inlineStr">
         <is>
           <t>https://ec.jnu.edu.cn/2024/1129/c42192a826585/page.htm</t>
         </is>
@@ -7054,7 +7043,7 @@
           <t>商学院</t>
         </is>
       </c>
-      <c r="F117" s="2" t="n">
+      <c r="F117" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G117" t="inlineStr">
@@ -7062,7 +7051,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H117" s="3" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>辽宁大学商学院2026年面向社会公开招聘3名高层次和急需紧缺人才公告（第二批）</t>
         </is>
@@ -7077,7 +7066,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K117" s="3" t="inlineStr">
+      <c r="K117" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/424265.html</t>
         </is>
@@ -7119,7 +7108,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H118" s="3" t="inlineStr">
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>辽宁大学商学院2026年高层次人才招聘公告（第二批）</t>
         </is>
@@ -7134,7 +7123,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K118" s="3" t="inlineStr">
+      <c r="K118" s="2" t="inlineStr">
         <is>
           <t>https://coba.lnu.edu.cn/info/1164/4976.htm</t>
         </is>
@@ -7172,7 +7161,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H119" s="3" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>闽江大学高层次人才引进相关招聘信息（校级方案参考）</t>
         </is>
@@ -7187,7 +7176,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K119" s="3" t="inlineStr">
+      <c r="K119" s="2" t="inlineStr">
         <is>
           <t>https://jsj.mju.edu.cn/2026/0529/c6083a219243/page.htm</t>
         </is>
@@ -7220,7 +7209,7 @@
           <t>???</t>
         </is>
       </c>
-      <c r="F120" s="2" t="n">
+      <c r="F120" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G120" t="inlineStr">
@@ -7228,7 +7217,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H120" s="3" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>2026年闽南师范大学引进高层次人才招聘方案（含商学院）</t>
         </is>
@@ -7243,7 +7232,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K120" s="3" t="inlineStr">
+      <c r="K120" s="2" t="inlineStr">
         <is>
           <t>https://rst.fujian.gov.cn/zw/ztzl/zxzt/sydwrczp/gccrczpfa/202603/t20260318_7113003.htm</t>
         </is>
@@ -7285,7 +7274,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H121" s="3" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>中央民族大学2026年度博士后招收公告</t>
         </is>
@@ -7300,7 +7289,7 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="K121" s="3" t="inlineStr">
+      <c r="K121" s="2" t="inlineStr">
         <is>
           <t>https://www.muc.edu.cn/info/1083/49048.htm</t>
         </is>
@@ -7337,12 +7326,15 @@
           <t>经济管理学院</t>
         </is>
       </c>
+      <c r="F122" s="3" t="n">
+        <v>46310</v>
+      </c>
       <c r="G122" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>南京农业大学经济管理学院2026年诚聘海内外优秀人才</t>
         </is>
@@ -7357,7 +7349,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K122" s="3" t="inlineStr">
+      <c r="K122" s="2" t="inlineStr">
         <is>
           <t>http://www.chinajxrc.com/gaoxiao/zpview_B5EAD67F114545E3.shtml</t>
         </is>
@@ -7404,7 +7396,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H123" s="3" t="inlineStr">
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>南京农业大学经济管理学院2026年诚聘海内外优秀人才</t>
         </is>
@@ -7419,7 +7411,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K123" s="3" t="inlineStr">
+      <c r="K123" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/425313.html</t>
         </is>
@@ -7462,7 +7454,7 @@
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
-      <c r="H124" s="3" t="inlineStr">
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>南京农业大学经济管理学院人才招聘公告</t>
         </is>
@@ -7477,7 +7469,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K124" s="3" t="inlineStr">
+      <c r="K124" s="2" t="inlineStr">
         <is>
           <t>https://economy.njau.edu.cn/info/1460/14471.htm</t>
         </is>
@@ -7520,7 +7512,7 @@
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
-      <c r="H125" s="3" t="inlineStr">
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>南京农业大学经济管理学院人才招聘公告（备份）</t>
         </is>
@@ -7535,7 +7527,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K125" s="3" t="inlineStr">
+      <c r="K125" s="2" t="inlineStr">
         <is>
           <t>https://economy.njau.edu.cn/info/1435/14470.htm</t>
         </is>
@@ -7572,17 +7564,14 @@
           <t>经济管理系</t>
         </is>
       </c>
-      <c r="F126" s="2" t="n">
-        <v>46001</v>
-      </c>
       <c r="G126" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H126" s="3" t="inlineStr">
-        <is>
-          <t>华北电力大学2026年度教学科研岗位招聘启事（保定）</t>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>华北电力大学2026年度教学科研岗位招聘启事</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7595,9 +7584,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K126" s="3" t="inlineStr">
-        <is>
-          <t>https://www.ncepu.edu.cn/rczp/bdrczp/c9e86b816a9e4c359d3bd2695f737a3a.htm</t>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncepu.edu.cn/rczp/bjrczp/e5222acc770e4a7cb8e09eefad9098e1.htm</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -7632,17 +7621,14 @@
           <t>经济管理系</t>
         </is>
       </c>
-      <c r="F127" s="2" t="n">
-        <v>46001</v>
-      </c>
       <c r="G127" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H127" s="3" t="inlineStr">
-        <is>
-          <t>华北电力大学2026年度教学科研岗位招聘启事（经管学院转载）</t>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>华北电力大学2026年度教学科研岗位招聘启事（保定）</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7655,9 +7641,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K127" s="3" t="inlineStr">
-        <is>
-          <t>https://business.ncepu.edu.cn/szll2/rczp/9ab45767dd944af290b7e2d4c0b41184.htm</t>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncepu.edu.cn/rczp/bdrczp/c9e86b816a9e4c359d3bd2695f737a3a.htm</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -7697,9 +7683,9 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>华北电力大学2026年度教学科研岗位招聘启事</t>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>华北电力大学2026年度教学科研岗位招聘启事（经管学院转载）</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7712,9 +7698,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K128" s="3" t="inlineStr">
-        <is>
-          <t>https://www.ncepu.edu.cn/rczp/bjrczp/e5222acc770e4a7cb8e09eefad9098e1.htm</t>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>https://business.ncepu.edu.cn/szll2/rczp/9ab45767dd944af290b7e2d4c0b41184.htm</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -7754,7 +7740,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H129" s="3" t="inlineStr">
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>东北大学2025年专任教师招聘启事</t>
         </is>
@@ -7769,7 +7755,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K129" s="3" t="inlineStr">
+      <c r="K129" s="2" t="inlineStr">
         <is>
           <t>https://rsc.neu.edu.cn/2025/0623/c3973a288430/page.htm</t>
         </is>
@@ -7811,7 +7797,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H130" s="3" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>南京理工大学2026年诚邀英才依托申报海外优青</t>
         </is>
@@ -7826,7 +7812,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K130" s="3" t="inlineStr">
+      <c r="K130" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/379023.html</t>
         </is>
@@ -7864,7 +7850,7 @@
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
-      <c r="H131" s="3" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>南京理工大学企业管理（经济管理学院-专任教师）</t>
         </is>
@@ -7879,7 +7865,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K131" s="3" t="inlineStr">
+      <c r="K131" s="2" t="inlineStr">
         <is>
           <t>https://www.sciencehr.net/job/228739.html</t>
         </is>
@@ -7917,7 +7903,7 @@
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
-      <c r="H132" s="3" t="inlineStr">
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>南京理工大学会计学（经济管理学院-专任教师）</t>
         </is>
@@ -7932,7 +7918,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K132" s="3" t="inlineStr">
+      <c r="K132" s="2" t="inlineStr">
         <is>
           <t>https://www.100zp.com/job/211061.html</t>
         </is>
@@ -7969,7 +7955,7 @@
           <t>商学院</t>
         </is>
       </c>
-      <c r="F133" s="2" t="n">
+      <c r="F133" s="3" t="n">
         <v>46385</v>
       </c>
       <c r="G133" t="inlineStr">
@@ -7977,7 +7963,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H133" s="3" t="inlineStr">
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>南京师范大学商学院2026年公开招聘2名工作人员公告（第二批）</t>
         </is>
@@ -7992,7 +7978,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K133" s="3" t="inlineStr">
+      <c r="K133" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/426065.html</t>
         </is>
@@ -8034,7 +8020,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H134" s="3" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>南航2026海外优青</t>
         </is>
@@ -8049,7 +8035,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K134" s="3" t="inlineStr">
+      <c r="K134" s="2" t="inlineStr">
         <is>
           <t>https://m.gaoxiaojob.com/announcement/detail/378911.html</t>
         </is>
@@ -8082,7 +8068,7 @@
           <t>经济学院</t>
         </is>
       </c>
-      <c r="F135" s="2" t="n">
+      <c r="F135" s="3" t="n">
         <v>46385</v>
       </c>
       <c r="G135" t="inlineStr">
@@ -8090,7 +8076,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H135" s="3" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>南京财经大学2026年公开招聘教学科研岗人员公告</t>
         </is>
@@ -8105,7 +8091,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K135" s="3" t="inlineStr">
+      <c r="K135" s="2" t="inlineStr">
         <is>
           <t>https://m.gaoxiaojob.com/announcement/detail/394111.html</t>
         </is>
@@ -8142,7 +8128,7 @@
           <t>商学院</t>
         </is>
       </c>
-      <c r="F136" s="2" t="n">
+      <c r="F136" s="3" t="n">
         <v>46445</v>
       </c>
       <c r="G136" t="inlineStr">
@@ -8150,7 +8136,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H136" s="3" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>南京大学商学院2026年招聘特任副研究员公告</t>
         </is>
@@ -8165,7 +8151,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K136" s="3" t="inlineStr">
+      <c r="K136" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/426520.html</t>
         </is>
@@ -8207,7 +8193,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H137" s="3" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>南京大学商学院2026年全球招募至诚人才信息</t>
         </is>
@@ -8222,7 +8208,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K137" s="3" t="inlineStr">
+      <c r="K137" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/434920.html</t>
         </is>
@@ -8269,7 +8255,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H138" s="3" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>南京大学商学院2026年度研究系列人员招聘公告</t>
         </is>
@@ -8284,7 +8270,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K138" s="3" t="inlineStr">
+      <c r="K138" s="2" t="inlineStr">
         <is>
           <t>https://nubs.nju.edu.cn/d9/7c/c17177a842108/page.htm</t>
         </is>
@@ -8331,7 +8317,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H139" s="3" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>南京大学商学院2026年度研究系列人员招聘公告(alt)</t>
         </is>
@@ -8346,7 +8332,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K139" s="3" t="inlineStr">
+      <c r="K139" s="2" t="inlineStr">
         <is>
           <t>https://nubs.nju.edu.cn/d9/72/c8896a842098/page.htm</t>
         </is>
@@ -8380,20 +8366,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>经济学院</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="n">
-        <v>45998</v>
+          <t>金融学院</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>南开大学经济学院2026年教学科研人员招聘启事</t>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>2026年南开大学青年学科带头人岗位岗位招聘公告（金融学院）</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8406,9 +8389,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K140" s="3" t="inlineStr">
-        <is>
-          <t>https://economics.nankai.edu.cn/2025/1120/c16001a584393/page.htm</t>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>https://finance.nankai.edu.cn/2026/0119/c34541a589287/page.htm</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -8440,20 +8423,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>经济学院</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="n">
-        <v>46009</v>
+          <t>商学院</t>
+        </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H141" s="3" t="inlineStr">
-        <is>
-          <t>南开大学经济学院2026年人才引进、教职工公开招聘、博士后招收公告</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>南开大学商学院诚聘全球英才</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8466,9 +8446,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K141" s="3" t="inlineStr">
-        <is>
-          <t>https://economics.nankai.edu.cn/2025/1211/c16001a586532/page.htm</t>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>https://nbr.nankai.edu.cn/nkglpl/news/view/20251106121718001</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -8500,20 +8480,22 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>金融学院</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="n">
-        <v>46031</v>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H142" s="3" t="inlineStr">
-        <is>
-          <t>金融学院2026年教学科研（副高）岗位招聘公告</t>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>南开大学经济学院2026年人才引进、教职工公开招聘、博士后招收公告</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8526,9 +8508,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K142" s="3" t="inlineStr">
-        <is>
-          <t>https://finance.nankai.edu.cn/2025/1219/c34541a587299/page.htm</t>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>https://economics.nankai.edu.cn/2025/1211/c16001a586532/page.htm</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -8560,7 +8542,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>金融学院</t>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -8568,9 +8555,9 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H143" s="3" t="inlineStr">
-        <is>
-          <t>2026年南开大学青年学科带头人岗位岗位招聘公告（金融学院）</t>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>南开大学经济学院2026年教学科研人员招聘启事</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8583,9 +8570,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K143" s="3" t="inlineStr">
-        <is>
-          <t>https://finance.nankai.edu.cn/2026/0119/c34541a589287/page.htm</t>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>https://economics.nankai.edu.cn/2025/1120/c16001a584393/page.htm</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -8617,17 +8604,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>商学院</t>
+          <t>金融学院</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="H144" s="3" t="inlineStr">
-        <is>
-          <t>南开大学商学院诚聘全球英才</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>金融学院2026年教学科研（副高）岗位招聘公告</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8640,9 +8627,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K144" s="3" t="inlineStr">
-        <is>
-          <t>https://nbr.nankai.edu.cn/nkglpl/news/view/20251106121718001</t>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>https://finance.nankai.edu.cn/2025/1219/c34541a587299/page.htm</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -8678,7 +8665,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H145" s="3" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>宁波大学2026年公开招聘全职博士后</t>
         </is>
@@ -8693,7 +8680,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K145" s="3" t="inlineStr">
+      <c r="K145" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/386397.html</t>
         </is>
@@ -8731,7 +8718,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H146" s="3" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>宁波大学2026年公开招聘高层次人才（教师）</t>
         </is>
@@ -8746,7 +8733,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K146" s="3" t="inlineStr">
+      <c r="K146" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/409898.html</t>
         </is>
@@ -8784,7 +8771,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H147" s="3" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>宁波大学2026年公开招聘高层次人才（教师）alt</t>
         </is>
@@ -8799,7 +8786,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K147" s="3" t="inlineStr">
+      <c r="K147" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/404723.html</t>
         </is>
@@ -8837,7 +8824,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H148" s="3" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>宁波大学2026年公开招聘高层次人才（教师）公告</t>
         </is>
@@ -8852,7 +8839,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K148" s="3" t="inlineStr">
+      <c r="K148" s="2" t="inlineStr">
         <is>
           <t>https://recruit.nbu.edu.cn/info/1009/2521.htm</t>
         </is>
@@ -8886,7 +8873,7 @@
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
-      <c r="H149" s="3" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>高层次人才招聘-宁波大学商学院</t>
         </is>
@@ -8901,7 +8888,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K149" s="3" t="inlineStr">
+      <c r="K149" s="2" t="inlineStr">
         <is>
           <t>https://nbubs.nbu.edu.cn/rczp/gccrczp.htm</t>
         </is>
@@ -8943,7 +8930,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H150" s="3" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>中国海洋大学2026年卓越博士后招聘公告</t>
         </is>
@@ -8958,7 +8945,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K150" s="3" t="inlineStr">
+      <c r="K150" s="2" t="inlineStr">
         <is>
           <t>https://rsc.ouc.edu.cn/2026/0914/c923a537132/page.htm</t>
         </is>
@@ -9000,7 +8987,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H151" s="3" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>中国海洋大学2026年科研博士后招聘启事</t>
         </is>
@@ -9015,7 +9002,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K151" s="3" t="inlineStr">
+      <c r="K151" s="2" t="inlineStr">
         <is>
           <t>https://rsc.ouc.edu.cn/2026/0630/c923a533385/page.htm</t>
         </is>
@@ -9062,7 +9049,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H152" s="3" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>北京大学汇丰商学院与顺丰科技联合培养博士后招聘启事（2026年度）</t>
         </is>
@@ -9077,7 +9064,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K152" s="3" t="inlineStr">
+      <c r="K152" s="2" t="inlineStr">
         <is>
           <t>https://www.phbs.pku.edu.cn/info/1471/163281.htm</t>
         </is>
@@ -9124,7 +9111,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H153" s="3" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>北京大学汇丰商学院人工智能管理研究中心博士后研究人员招聘启事（2026年）</t>
         </is>
@@ -9139,7 +9126,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K153" s="3" t="inlineStr">
+      <c r="K153" s="2" t="inlineStr">
         <is>
           <t>https://www.phbs.pku.edu.cn/info/1471/163301.htm</t>
         </is>
@@ -9177,7 +9164,7 @@
         </is>
       </c>
       <c r="G154" t="inlineStr"/>
-      <c r="H154" s="3" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>北京大学汇丰商学院教师招聘</t>
         </is>
@@ -9192,7 +9179,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K154" s="3" t="inlineStr">
+      <c r="K154" s="2" t="inlineStr">
         <is>
           <t>https://www.phbs.pku.edu.cn/info/1451/129371.htm</t>
         </is>
@@ -9230,7 +9217,7 @@
         </is>
       </c>
       <c r="G155" t="inlineStr"/>
-      <c r="H155" s="3" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>北京大学汇丰商学院数字金融方向博士后招聘启事</t>
         </is>
@@ -9245,7 +9232,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K155" s="3" t="inlineStr">
+      <c r="K155" s="2" t="inlineStr">
         <is>
           <t>https://www.phbs.pku.edu.cn/info/1471/179281.htm</t>
         </is>
@@ -9279,20 +9266,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>经济学院</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="n">
-        <v>45747</v>
+          <t>光华管理学院</t>
+        </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>2025年北京大学经济学院教学科研岗位招聘启事</t>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>2025年北京大学光华管理学院教学科研岗位招聘启事</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9305,14 +9289,14 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K156" s="3" t="inlineStr">
-        <is>
-          <t>https://hr.pku.edu.cn/rczp/jxky/f5471d5b1df745db9ff270ba2f4fc7db.htm</t>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>https://hr.pku.edu.cn/rczp/jxky/a92f835c47714f1ababadf98678a5085.htm</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>econ_pku_hr@163.com</t>
+          <t>recruitment@gsm.pku.edu.cn</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -9347,17 +9331,14 @@
           <t>经济学院</t>
         </is>
       </c>
-      <c r="F157" s="2" t="n">
-        <v>45991</v>
-      </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H157" s="3" t="inlineStr">
-        <is>
-          <t>北京大学经济学院2026年教职招聘通知</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>2025年北京大学经济学院教学科研岗位招聘启事</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -9370,9 +9351,14 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K157" s="3" t="inlineStr">
-        <is>
-          <t>https://econ.pku.edu.cn/tzgg/50170econ391389.htm</t>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>https://hr.pku.edu.cn/rczp/jxky/f5471d5b1df745db9ff270ba2f4fc7db.htm</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>econ_pku_hr@163.com</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -9409,12 +9395,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>2025年北京大学光华管理学院教学科研岗位招聘启事</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>2026年北京大学光华管理学院教学科研岗位招聘启事</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9427,9 +9413,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K158" s="3" t="inlineStr">
-        <is>
-          <t>https://hr.pku.edu.cn/rczp/jxky/a92f835c47714f1ababadf98678a5085.htm</t>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>https://hr.pku.edu.cn/rczp/jxky/5a8411beae2c4e8ba518ba4c6efe8794.htm</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -9466,7 +9452,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>光华管理学院</t>
+          <t>经济学院</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -9474,9 +9460,9 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H159" s="3" t="inlineStr">
-        <is>
-          <t>2026年北京大学光华管理学院教学科研岗位招聘启事</t>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>2026年北京大学经济学院教学科研岗位招聘启事</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9489,14 +9475,14 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K159" s="3" t="inlineStr">
-        <is>
-          <t>https://hr.pku.edu.cn/rczp/jxky/5a8411beae2c4e8ba518ba4c6efe8794.htm</t>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>https://hr.pku.edu.cn/rczp/jxky/aba345dfa9d040df8b64488f3af5b37a.htm</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>recruitment@gsm.pku.edu.cn</t>
+          <t>econ_pku_hr@163.com</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -9536,9 +9522,9 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H160" s="3" t="inlineStr">
-        <is>
-          <t>2026年北京大学经济学院教学科研岗位招聘启事</t>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>北京大学经济学院2026年教职招聘通知</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9551,14 +9537,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K160" s="3" t="inlineStr">
-        <is>
-          <t>https://hr.pku.edu.cn/rczp/jxky/aba345dfa9d040df8b64488f3af5b37a.htm</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>econ_pku_hr@163.com</t>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>https://econ.pku.edu.cn/tzgg/50170econ391389.htm</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -9594,7 +9575,7 @@
         </is>
       </c>
       <c r="G161" t="inlineStr"/>
-      <c r="H161" s="3" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>北京大学经济学院“奥园博士后”项目申请公告</t>
         </is>
@@ -9609,7 +9590,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K161" s="3" t="inlineStr">
+      <c r="K161" s="2" t="inlineStr">
         <is>
           <t>https://econ.pku.edu.cn/tzgg/50170econ372315.htm</t>
         </is>
@@ -9647,7 +9628,7 @@
         </is>
       </c>
       <c r="G162" t="inlineStr"/>
-      <c r="H162" s="3" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>北京大学经济学院面向海内外诚聘英才</t>
         </is>
@@ -9662,7 +9643,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K162" s="3" t="inlineStr">
+      <c r="K162" s="2" t="inlineStr">
         <is>
           <t>https://econ.pku.edu.cn/tzgg/334008.htm</t>
         </is>
@@ -9700,7 +9681,7 @@
           <t>商学院</t>
         </is>
       </c>
-      <c r="F163" s="2" t="n">
+      <c r="F163" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G163" t="inlineStr">
@@ -9708,7 +9689,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H163" s="3" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>2026年莆田学院公开招聘博士高层次人才方案</t>
         </is>
@@ -9723,7 +9704,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K163" s="3" t="inlineStr">
+      <c r="K163" s="2" t="inlineStr">
         <is>
           <t>https://www.ptu.edu.cn/info/1024/26914.htm</t>
         </is>
@@ -9766,7 +9747,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H164" s="3" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>2026年泉州师范学院公开招聘高层次人才方案（含商学院）</t>
         </is>
@@ -9781,7 +9762,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K164" s="3" t="inlineStr">
+      <c r="K164" s="2" t="inlineStr">
         <is>
           <t>https://www.qztc.edu.cn/2026/0804/c2094a294909/page.htm</t>
         </is>
@@ -9815,20 +9796,20 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>财政金融学院</t>
-        </is>
-      </c>
-      <c r="F165" s="2" t="n">
-        <v>45981</v>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>46387</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H165" s="3" t="inlineStr">
-        <is>
-          <t>中国人民大学财政金融学院2026年度引进人才和教师通知</t>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>中国人民大学商学院年度教师招聘（滚动至2026-12-31）</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -9841,19 +9822,19 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K165" s="3" t="inlineStr">
-        <is>
-          <t>https://ifegg.com/html/11188.html</t>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rmbs.ruc.edu.cn/szyky/rczp/ndjszp/97756c032dac49fab16e5a273f0ebf9d.htm</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>cjzonghe@ruc.edu.cn</t>
+          <t>recruitment@rmbs.ruc.edu.cn</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -9880,40 +9861,33 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>财政金融学院/经济学院</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="n">
-        <v>45981</v>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>独树一帜走新路 汇聚英才谱新篇——关于中国人民大学2026年度人才引进和教师招聘通知</t>
+          <t>应用经济学院</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>中国人民大学应用经济学院博士后招聘公告</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>含财政金融学院、经济学院等</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="K166" s="3" t="inlineStr">
-        <is>
-          <t>http://hr.ruc.edu.cn/zpxx/c26637043fc8457496f0781066bcad04.htm</t>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>http://ae.ruc.edu.cn/xwzx/tzgg/62a1d3280023497a9cc7a2c15c5894c7.htm</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -9943,17 +9917,19 @@
           <t>财政金融学院</t>
         </is>
       </c>
-      <c r="F167" s="2" t="n">
-        <v>45981</v>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H167" s="3" t="inlineStr">
-        <is>
-          <t>财政金融学院2026年度人才引进和教师招聘通知</t>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>中国人民大学财政金融学院2026年度引进人才和教师通知</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -9966,9 +9942,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K167" s="3" t="inlineStr">
-        <is>
-          <t>http://sf.ruc.edu.cn/sylm/gg_sy/gg/67fefa2748ef4125aa908c2f3bfed087.htm</t>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>https://ifegg.com/html/11188.html</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -9978,7 +9954,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -10005,12 +9981,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>商学院</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Rolling</t>
+          <t>财政金融学院/经济学院</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -10018,29 +9989,24 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H168" s="3" t="inlineStr">
-        <is>
-          <t>中国人民大学商学院年度教师招聘（滚动至2026-12-31）</t>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>独树一帜走新路 汇聚英才谱新篇——关于中国人民大学2026年度人才引进和教师招聘通知</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>滚动招聘，招满即止</t>
+          <t>含财政金融学院、经济学院等</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Dept/HR</t>
-        </is>
-      </c>
-      <c r="K168" s="3" t="inlineStr">
-        <is>
-          <t>https://www.rmbs.ruc.edu.cn/szyky/rczp/ndjszp/97756c032dac49fab16e5a273f0ebf9d.htm</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>recruitment@rmbs.ruc.edu.cn</t>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>http://hr.ruc.edu.cn/zpxx/c26637043fc8457496f0781066bcad04.htm</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -10072,18 +10038,27 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>应用经济学院</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" s="3" t="inlineStr">
-        <is>
-          <t>中国人民大学应用经济学院博士后招聘公告</t>
+          <t>财政金融学院</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>财政金融学院2026年度人才引进和教师招聘通知</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>滚动招聘，招满即止</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -10091,14 +10066,19 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K169" s="3" t="inlineStr">
-        <is>
-          <t>http://ae.ruc.edu.cn/xwzx/tzgg/62a1d3280023497a9cc7a2c15c5894c7.htm</t>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>http://sf.ruc.edu.cn/sylm/gg_sy/gg/67fefa2748ef4125aa908c2f3bfed087.htm</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>cjzonghe@ruc.edu.cn</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10109,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H170" s="3" t="inlineStr">
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>华南农业大学经济管理学院姜百臣教授研究团队招聘博士后启事</t>
         </is>
@@ -10144,7 +10124,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K170" s="3" t="inlineStr">
+      <c r="K170" s="2" t="inlineStr">
         <is>
           <t>https://cem.scau.edu.cn/2025/0221/c9875a399607/page.htm</t>
         </is>
@@ -10182,7 +10162,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H171" s="3" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>华南农业大学经济管理学院易法敏教授研究团队招聘博士后</t>
         </is>
@@ -10197,7 +10177,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K171" s="3" t="inlineStr">
+      <c r="K171" s="2" t="inlineStr">
         <is>
           <t>https://cem.scau.edu.cn/2025/0221/c9875a399618/page.htm</t>
         </is>
@@ -10235,7 +10215,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H172" s="3" t="inlineStr">
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>华南农业大学经济管理学院杨学儒教授研究团队招聘博士后启事</t>
         </is>
@@ -10250,7 +10230,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K172" s="3" t="inlineStr">
+      <c r="K172" s="2" t="inlineStr">
         <is>
           <t>https://cem.scau.edu.cn/2025/0221/c9875a399608/page.htm</t>
         </is>
@@ -10288,7 +10268,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H173" s="3" t="inlineStr">
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>华南农业大学经济管理学院柳松教授研究团队招聘博士后启事</t>
         </is>
@@ -10303,7 +10283,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K173" s="3" t="inlineStr">
+      <c r="K173" s="2" t="inlineStr">
         <is>
           <t>https://cem.scau.edu.cn/2025/0221/c9875a399594/page.htm</t>
         </is>
@@ -10341,7 +10321,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H174" s="3" t="inlineStr">
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>华南农业大学经济管理学院段伟教授研究团队招聘博士后启事</t>
         </is>
@@ -10356,7 +10336,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K174" s="3" t="inlineStr">
+      <c r="K174" s="2" t="inlineStr">
         <is>
           <t>https://cem.scau.edu.cn/2025/0221/c9875a399586/page.htm</t>
         </is>
@@ -10393,15 +10373,12 @@
           <t>经济与管理学院</t>
         </is>
       </c>
-      <c r="F175" s="2" t="n">
-        <v>45905</v>
-      </c>
       <c r="G175" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="H175" s="3" t="inlineStr">
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>华南师范大学2025年公开招聘教学科研人员公告</t>
         </is>
@@ -10416,7 +10393,7 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="K175" s="3" t="inlineStr">
+      <c r="K175" s="2" t="inlineStr">
         <is>
           <t>http://em.scnu.edu.cn/a/20250910/10765.html</t>
         </is>
@@ -10449,12 +10426,15 @@
           <t>????</t>
         </is>
       </c>
+      <c r="F176" s="3" t="n">
+        <v>46387</v>
+      </c>
       <c r="G176" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H176" s="3" t="inlineStr">
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>山东财经大学2026年度高层次人才和优秀博士招聘公告</t>
         </is>
@@ -10469,7 +10449,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K176" s="3" t="inlineStr">
+      <c r="K176" s="2" t="inlineStr">
         <is>
           <t>https://www.sdufe.edu.cn/info/1068/26223.htm</t>
         </is>
@@ -10507,7 +10487,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H177" s="3" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>山东财经大学经济学院2025年全职博士后研究人员招聘简章</t>
         </is>
@@ -10522,7 +10502,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K177" s="3" t="inlineStr">
+      <c r="K177" s="2" t="inlineStr">
         <is>
           <t>https://econ.sdufe.edu.cn/info/1058/7192.htm</t>
         </is>
@@ -10560,7 +10540,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H178" s="3" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>山东财经大学金融学院2026年全职博士后研究人员招聘公告</t>
         </is>
@@ -10575,7 +10555,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K178" s="3" t="inlineStr">
+      <c r="K178" s="2" t="inlineStr">
         <is>
           <t>https://jinrong.sdufe.edu.cn/info/1160/8909.htm</t>
         </is>
@@ -10613,7 +10593,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H179" s="3" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>山东财经大学金融学院2026年招聘全职博士后研究人员公告-博士后招聘网</t>
         </is>
@@ -10628,7 +10608,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K179" s="3" t="inlineStr">
+      <c r="K179" s="2" t="inlineStr">
         <is>
           <t>http://www.boshihoujob.com/gxbsh/shandong/131224.html</t>
         </is>
@@ -10662,16 +10642,20 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>中银科技金融学院</t>
-        </is>
-      </c>
-      <c r="F180" s="2" t="n">
-        <v>46356</v>
-      </c>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" s="3" t="inlineStr">
-        <is>
-          <t>上海交通大学中银科技金融学院诚聘天下英才</t>
+          <t>安泰经济与管理学院/会计系</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="n">
+        <v>46341</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>会计系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -10684,9 +10668,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K180" s="3" t="inlineStr">
-        <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97786.html</t>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97769.html</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -10718,20 +10702,20 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院/信息技术与创新系</t>
-        </is>
-      </c>
-      <c r="F181" s="2" t="n">
-        <v>46357</v>
+          <t>安泰经济与管理学院/经济系</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="n">
+        <v>46341</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="H181" s="3" t="inlineStr">
-        <is>
-          <t>信息、技术与创新系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>经济系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -10744,9 +10728,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K181" s="3" t="inlineStr">
-        <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97772.html</t>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97812.html</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -10778,22 +10762,20 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院/会计系</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>Rolling</t>
-        </is>
+          <t>安泰经济与管理学院/金融系</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="n">
+        <v>46341</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="H182" s="3" t="inlineStr">
-        <is>
-          <t>会计系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>金融系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -10806,9 +10788,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K182" s="3" t="inlineStr">
-        <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97769.html</t>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97771.html</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -10840,17 +10822,16 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院/数据与商务智能系</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="H183" s="3" t="inlineStr">
-        <is>
-          <t>数据与商务智能系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+          <t>中银科技金融学院</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="n">
+        <v>46356</v>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>上海交通大学中银科技金融学院诚聘天下英才</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -10863,9 +10844,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K183" s="3" t="inlineStr">
-        <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97770.html</t>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97786.html</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -10897,13 +10878,20 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" s="3" t="inlineStr">
-        <is>
-          <t>海外优青 | 欢迎依托上海交大安泰经济与管理学院申报</t>
+          <t>安泰经济与管理学院/数据与商务智能系</t>
+        </is>
+      </c>
+      <c r="F184" s="3" t="n">
+        <v>46356</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>数据与商务智能系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -10916,14 +10904,14 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K184" s="3" t="inlineStr">
-        <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/94461.html</t>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97770.html</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -10950,17 +10938,20 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院/管理科学系</t>
-        </is>
+          <t>安泰经济与管理学院/信息技术与创新系</t>
+        </is>
+      </c>
+      <c r="F185" s="3" t="n">
+        <v>46357</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="H185" s="3" t="inlineStr">
-        <is>
-          <t>管理科学系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>信息、技术与创新系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -10973,9 +10964,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K185" s="3" t="inlineStr">
-        <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97783.html</t>
+      <c r="K185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97772.html</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -11007,17 +10998,20 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院/组织管理系</t>
-        </is>
+          <t>安泰经济与管理学院/管理科学系</t>
+        </is>
+      </c>
+      <c r="F186" s="3" t="n">
+        <v>46357</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="H186" s="3" t="inlineStr">
-        <is>
-          <t>组织管理系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>管理科学系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11030,9 +11024,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K186" s="3" t="inlineStr">
-        <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97785.html</t>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97783.html</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -11064,17 +11058,13 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院/经济系</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="H187" s="3" t="inlineStr">
-        <is>
-          <t>经济系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+          <t>安泰经济与管理学院</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>海外优青 | 欢迎依托上海交大安泰经济与管理学院申报</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11087,14 +11077,14 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K187" s="3" t="inlineStr">
-        <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97812.html</t>
+      <c r="K187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/94461.html</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -11121,7 +11111,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院/金融系</t>
+          <t>安泰经济与管理学院/组织管理系</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -11129,9 +11119,9 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="H188" s="3" t="inlineStr">
-        <is>
-          <t>金融系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>组织管理系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11144,9 +11134,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K188" s="3" t="inlineStr">
-        <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97771.html</t>
+      <c r="K188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97785.html</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -11182,7 +11172,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H189" s="3" t="inlineStr">
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>深圳北理莫斯科大学2026年管理系招聘公告（含数字经济/财务管理）</t>
         </is>
@@ -11197,7 +11187,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K189" s="3" t="inlineStr">
+      <c r="K189" s="2" t="inlineStr">
         <is>
           <t>https://www.smbu.edu.cn/info/4561/129821.htm</t>
         </is>
@@ -11239,7 +11229,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H190" s="3" t="inlineStr">
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>2026上海财经大学商学院世界经济与贸易系、产业经济系师资招聘</t>
         </is>
@@ -11254,7 +11244,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K190" s="3" t="inlineStr">
+      <c r="K190" s="2" t="inlineStr">
         <is>
           <t>https://cob.sufe.edu.cn/Home/Detail/26953</t>
         </is>
@@ -11301,7 +11291,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H191" s="3" t="inlineStr">
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>上海财经大学统计与数据科学学院面向全球诚聘英才（Faculty Recruitment，2026）</t>
         </is>
@@ -11316,7 +11306,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K191" s="3" t="inlineStr">
+      <c r="K191" s="2" t="inlineStr">
         <is>
           <t>https://ibdr.sufe.edu.cn/e0/17/c19471a253975/page.htm</t>
         </is>
@@ -11363,7 +11353,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H192" s="3" t="inlineStr">
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>上海财经大学金融学院2026年“毓秀人才计划”招聘启事</t>
         </is>
@@ -11378,7 +11368,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K192" s="3" t="inlineStr">
+      <c r="K192" s="2" t="inlineStr">
         <is>
           <t>https://sof.sufe.edu.cn/d1/50/c7791a250192/page.htm</t>
         </is>
@@ -11421,7 +11411,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H193" s="3" t="inlineStr">
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>上海对外经贸大学国际组织学院（贸易谈判学院）2026年诚聘海内外英才</t>
         </is>
@@ -11436,7 +11426,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K193" s="3" t="inlineStr">
+      <c r="K193" s="2" t="inlineStr">
         <is>
           <t>https://www.suibe.edu.cn/gjzz/2025/0421/c21874a183262/page.htm</t>
         </is>
@@ -11474,7 +11464,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H194" s="3" t="inlineStr">
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>上海对外经贸大学教学科研岗位人才招聘启事</t>
         </is>
@@ -11489,7 +11479,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K194" s="3" t="inlineStr">
+      <c r="K194" s="2" t="inlineStr">
         <is>
           <t>https://www.suibe.edu.cn/rsc/2025/0401/c3652a182425/page.htm</t>
         </is>
@@ -11522,7 +11512,7 @@
           <t>风险分析预测与管控研究院</t>
         </is>
       </c>
-      <c r="F195" s="2" t="n">
+      <c r="F195" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G195" t="inlineStr">
@@ -11530,7 +11520,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H195" s="3" t="inlineStr">
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>南方科技大学风险分析预测与管控研究院2026年招聘博士后</t>
         </is>
@@ -11545,7 +11535,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K195" s="3" t="inlineStr">
+      <c r="K195" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/402555.html</t>
         </is>
@@ -11583,7 +11573,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H196" s="3" t="inlineStr">
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>Recruiting Statement SUSTech Business School 2026</t>
         </is>
@@ -11598,7 +11588,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K196" s="3" t="inlineStr">
+      <c r="K196" s="2" t="inlineStr">
         <is>
           <t>https://business.sustech.edu.cn/web/job_detail.php?id=21</t>
         </is>
@@ -11636,7 +11626,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H197" s="3" t="inlineStr">
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>南方科技大学古嘉雯金融数学及运筹管理课题组2026年博士后招聘启事</t>
         </is>
@@ -11651,7 +11641,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K197" s="3" t="inlineStr">
+      <c r="K197" s="2" t="inlineStr">
         <is>
           <t>http://boshihoujob.com/gxbsh/guangdong/131967.html</t>
         </is>
@@ -11689,7 +11679,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H198" s="3" t="inlineStr">
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>南方科技大学风险分析预测与管控研究院2026年博士后招聘</t>
         </is>
@@ -11704,7 +11694,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K198" s="3" t="inlineStr">
+      <c r="K198" s="2" t="inlineStr">
         <is>
           <t>http://boshihoujob.com/gxbsh/guangdong/131857.html</t>
         </is>
@@ -11741,13 +11731,19 @@
           <t>经济学院</t>
         </is>
       </c>
-      <c r="F199" s="2" t="n">
-        <v>45991</v>
-      </c>
-      <c r="G199" t="inlineStr"/>
-      <c r="H199" s="3" t="inlineStr">
-        <is>
-          <t>山东大学经济学院诚聘海内外英才</t>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>2025年度山东大学经济学院博士后招聘公告</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -11760,14 +11756,14 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K199" s="3" t="inlineStr">
-        <is>
-          <t>https://www.econ.sdu.edu.cn/info/1284/13146.htm</t>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.econ.sdu.edu.cn/info/1284/12952.htm</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11800,12 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="H200" s="3" t="inlineStr">
-        <is>
-          <t>2025年度山东大学经济学院博士后招聘公告</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>2026年度山东大学经济学院博士后招聘公告</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -11822,9 +11818,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K200" s="3" t="inlineStr">
-        <is>
-          <t>https://www.econ.sdu.edu.cn/info/1284/12952.htm</t>
+      <c r="K200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.econ.sdu.edu.cn/info/1284/13398.htm</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -11866,12 +11862,12 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H201" s="3" t="inlineStr">
-        <is>
-          <t>2026年度山东大学经济学院博士后招聘公告</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>山东大学经济学院2025年度教师招聘公告</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -11884,14 +11880,14 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K201" s="3" t="inlineStr">
-        <is>
-          <t>https://www.econ.sdu.edu.cn/info/1284/13398.htm</t>
+      <c r="K201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.econ.sdu.edu.cn/info/1284/11073.htm</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -11921,19 +11917,10 @@
           <t>经济学院</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>Rolling</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="H202" s="3" t="inlineStr">
-        <is>
-          <t>山东大学经济学院2025年度教师招聘公告</t>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>山东大学经济学院诚聘海内外英才</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -11946,9 +11933,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K202" s="3" t="inlineStr">
-        <is>
-          <t>https://www.econ.sdu.edu.cn/info/1284/11073.htm</t>
+      <c r="K202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.econ.sdu.edu.cn/info/1284/13146.htm</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -11983,7 +11970,7 @@
           <t>经济学院</t>
         </is>
       </c>
-      <c r="F203" s="2" t="n">
+      <c r="F203" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G203" t="inlineStr">
@@ -11991,7 +11978,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H203" s="3" t="inlineStr">
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>上海大学经济学院2026年招聘1名数量经济学教师</t>
         </is>
@@ -12006,7 +11993,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K203" s="3" t="inlineStr">
+      <c r="K203" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/370987.html</t>
         </is>
@@ -12043,11 +12030,11 @@
           <t>经济学院</t>
         </is>
       </c>
-      <c r="F204" s="2" t="n">
+      <c r="F204" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G204" t="inlineStr"/>
-      <c r="H204" s="3" t="inlineStr">
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>经济学院数字经济与贸易教师岗位</t>
         </is>
@@ -12062,7 +12049,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K204" s="3" t="inlineStr">
+      <c r="K204" s="2" t="inlineStr">
         <is>
           <t>https://jobs.shu.edu.cn/Ads/Ads?a=ff3d6c5d-27b3-4094-bb0c-f0ab7a5c945f</t>
         </is>
@@ -12100,7 +12087,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H205" s="3" t="inlineStr">
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>Faculty Openings at ShanghaiTech SEM</t>
         </is>
@@ -12115,7 +12102,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K205" s="3" t="inlineStr">
+      <c r="K205" s="2" t="inlineStr">
         <is>
           <t>https://sem.shanghaitech.edu.cn/sem_en/2026/0922/c3708a1127557/page.htm</t>
         </is>
@@ -12158,7 +12145,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H206" s="3" t="inlineStr">
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>上海科技大学创业与管理学院诚聘英才</t>
         </is>
@@ -12173,7 +12160,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K206" s="3" t="inlineStr">
+      <c r="K206" s="2" t="inlineStr">
         <is>
           <t>https://sem.shanghaitech.edu.cn/2026/0922/c3517a1127559/page.htm</t>
         </is>
@@ -12211,7 +12198,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H207" s="3" t="inlineStr">
+      <c r="H207" s="2" t="inlineStr">
         <is>
           <t>上海科技大学创业与管理学院诚聘英才（2026）</t>
         </is>
@@ -12226,7 +12213,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K207" s="3" t="inlineStr">
+      <c r="K207" s="2" t="inlineStr">
         <is>
           <t>https://sem.shanghaitech.edu.cn/2026/0922/c3518a1127559/page.htm</t>
         </is>
@@ -12270,7 +12257,7 @@
         </is>
       </c>
       <c r="G208" t="inlineStr"/>
-      <c r="H208" s="3" t="inlineStr">
+      <c r="H208" s="2" t="inlineStr">
         <is>
           <t>汕头大学商学院博士后招聘（数字经济/宏观经济/产业经济）</t>
         </is>
@@ -12285,7 +12272,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K208" s="3" t="inlineStr">
+      <c r="K208" s="2" t="inlineStr">
         <is>
           <t>https://biz.stu.edu.cn/gk/cpyc/bshzp.htm</t>
         </is>
@@ -12324,7 +12311,7 @@
         </is>
       </c>
       <c r="G209" t="inlineStr"/>
-      <c r="H209" s="3" t="inlineStr">
+      <c r="H209" s="2" t="inlineStr">
         <is>
           <t>汕头大学商学院教师招聘（含应用经济学/数字经济）</t>
         </is>
@@ -12339,7 +12326,7 @@
           <t>Online/Email</t>
         </is>
       </c>
-      <c r="K209" s="3" t="inlineStr">
+      <c r="K209" s="2" t="inlineStr">
         <is>
           <t>https://biz.stu.edu.cn/gk/cpyc/jszp.htm</t>
         </is>
@@ -12377,11 +12364,11 @@
           <t>经济学院</t>
         </is>
       </c>
-      <c r="F210" s="2" t="n">
+      <c r="F210" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G210" t="inlineStr"/>
-      <c r="H210" s="3" t="inlineStr">
+      <c r="H210" s="2" t="inlineStr">
         <is>
           <t>深圳大学经济学院米旭明教授团队博士后招聘-深圳大学人力资源部</t>
         </is>
@@ -12396,7 +12383,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K210" s="3" t="inlineStr">
+      <c r="K210" s="2" t="inlineStr">
         <is>
           <t>https://hr.szu.edu.cn/info/1070/23361.htm</t>
         </is>
@@ -12429,12 +12416,15 @@
           <t>经济管理学院</t>
         </is>
       </c>
+      <c r="F211" s="3" t="n">
+        <v>46310</v>
+      </c>
       <c r="G211" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H211" s="3" t="inlineStr">
+      <c r="H211" s="2" t="inlineStr">
         <is>
           <t>石家庄铁道大学2026年公开选聘14名工作人员公告</t>
         </is>
@@ -12449,7 +12439,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K211" s="3" t="inlineStr">
+      <c r="K211" s="2" t="inlineStr">
         <is>
           <t>https://460.net.cn/a/522403.html</t>
         </is>
@@ -12496,7 +12486,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H212" s="3" t="inlineStr">
+      <c r="H212" s="2" t="inlineStr">
         <is>
           <t>苏州大学2026年度热忱邀请全球英才依托申报海外优青项目</t>
         </is>
@@ -12511,7 +12501,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K212" s="3" t="inlineStr">
+      <c r="K212" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/373883.html</t>
         </is>
@@ -12558,7 +12548,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H213" s="3" t="inlineStr">
+      <c r="H213" s="2" t="inlineStr">
         <is>
           <t>苏州大学2026年面向全球招募275名博士后</t>
         </is>
@@ -12573,7 +12563,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K213" s="3" t="inlineStr">
+      <c r="K213" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/416991.html</t>
         </is>
@@ -12607,7 +12597,7 @@
         </is>
       </c>
       <c r="G214" t="inlineStr"/>
-      <c r="H214" s="3" t="inlineStr">
+      <c r="H214" s="2" t="inlineStr">
         <is>
           <t>华南师范大学经济与管理学院博士后流动站常年招收（理论/应用经济学）</t>
         </is>
@@ -12622,7 +12612,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K214" s="3" t="inlineStr">
+      <c r="K214" s="2" t="inlineStr">
         <is>
           <t>http://em.scnu.edu.cn/xueshukeyan/boshihouliudongzhan/</t>
         </is>
@@ -12664,8 +12654,11 @@
           <t>经济管理学院</t>
         </is>
       </c>
+      <c r="F215" s="3" t="n">
+        <v>46540</v>
+      </c>
       <c r="G215" t="inlineStr"/>
-      <c r="H215" s="3" t="inlineStr">
+      <c r="H215" s="2" t="inlineStr">
         <is>
           <t>IACMR 东南大学经济管理学院诚聘海内外英才</t>
         </is>
@@ -12680,7 +12673,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K215" s="3" t="inlineStr">
+      <c r="K215" s="2" t="inlineStr">
         <is>
           <t>https://iacmr.org/%E6%8B%9B%E8%81%98%E4%BF%A1%E6%81%AF%EF%BD%9C%E4%B8%9C%E5%8D%97%E5%A4%A7%E5%AD%A6%E7%BB%8F%E6%B5%8E%E7%AE%A1%E7%90%86%E5%AD%A6%E9%99%A2%E8%AF%9A%E8%81%98%E6%B5%B7%E5%86%85%E5%A4%96%E8%8B%B1%E6%89%8D/</t>
         </is>
@@ -12722,7 +12715,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H216" s="3" t="inlineStr">
+      <c r="H216" s="2" t="inlineStr">
         <is>
           <t>东南大学2026年诚邀全球全职博士后</t>
         </is>
@@ -12737,7 +12730,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K216" s="3" t="inlineStr">
+      <c r="K216" s="2" t="inlineStr">
         <is>
           <t>https://m.gaoxiaojob.com/announcement/detail/401115.html</t>
         </is>
@@ -12779,7 +12772,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H217" s="3" t="inlineStr">
+      <c r="H217" s="2" t="inlineStr">
         <is>
           <t>东南大学经管学院2026年人才招聘专区</t>
         </is>
@@ -12794,7 +12787,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K217" s="3" t="inlineStr">
+      <c r="K217" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/company/detail/31523.html</t>
         </is>
@@ -12836,7 +12829,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H218" s="3" t="inlineStr">
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t>东南大学经管学院诚聘海内外英才（2025长年有效）</t>
         </is>
@@ -12851,7 +12844,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K218" s="3" t="inlineStr">
+      <c r="K218" s="2" t="inlineStr">
         <is>
           <t>https://em.seu.edu.cn/2025/0303/c34068a520025/page.htm</t>
         </is>
@@ -12894,7 +12887,7 @@
         </is>
       </c>
       <c r="G219" t="inlineStr"/>
-      <c r="H219" s="3" t="inlineStr">
+      <c r="H219" s="2" t="inlineStr">
         <is>
           <t>中山大学国际金融学院诚聘海内外英才（教师+博士后）</t>
         </is>
@@ -12909,7 +12902,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K219" s="3" t="inlineStr">
+      <c r="K219" s="2" t="inlineStr">
         <is>
           <t>https://isbf.sysu.edu.cn/zh-hans/article/2827</t>
         </is>
@@ -12956,7 +12949,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H220" s="3" t="inlineStr">
+      <c r="H220" s="2" t="inlineStr">
         <is>
           <t>中山大学岭南学院2026年招聘教师（含教研岗与博士后）</t>
         </is>
@@ -12971,7 +12964,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K220" s="3" t="inlineStr">
+      <c r="K220" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/434822.html</t>
         </is>
@@ -13013,13 +13006,17 @@
           <t>经济学院</t>
         </is>
       </c>
-      <c r="F221" s="2" t="n">
-        <v>46059</v>
-      </c>
-      <c r="G221" t="inlineStr"/>
-      <c r="H221" s="3" t="inlineStr">
-        <is>
-          <t>天津师范大学数量经济学经济学院教师岗招聘</t>
+      <c r="F221" s="3" t="n">
+        <v>46387</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>2026年天津师范大学第一批招聘（博士层次专业技术岗位）公告</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13032,9 +13029,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K221" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sciencehr.net/job/208814.html</t>
+      <c r="K221" s="2" t="inlineStr">
+        <is>
+          <t>http://www.jiaoshizhaopin.net/tianjin/jobshow_511040.html</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -13069,17 +13066,10 @@
           <t>经济学院</t>
         </is>
       </c>
-      <c r="F222" s="2" t="n">
-        <v>46387</v>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H222" s="3" t="inlineStr">
-        <is>
-          <t>2026年天津师范大学第一批招聘（博士层次专业技术岗位）公告</t>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>天津师范大学数量经济学经济学院教师岗招聘</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -13092,9 +13082,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K222" s="3" t="inlineStr">
-        <is>
-          <t>http://www.jiaoshizhaopin.net/tianjin/jobshow_511040.html</t>
+      <c r="K222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencehr.net/job/208814.html</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -13134,7 +13124,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H223" s="3" t="inlineStr">
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>天津大学管理与经济学部2026年诚邀英才依托申报海外优青项目</t>
         </is>
@@ -13149,7 +13139,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K223" s="3" t="inlineStr">
+      <c r="K223" s="2" t="inlineStr">
         <is>
           <t>https://www.gxszw.com/region/tianjin/gxzptj/202601/30123168.html</t>
         </is>
@@ -13187,7 +13177,7 @@
         </is>
       </c>
       <c r="G224" t="inlineStr"/>
-      <c r="H224" s="3" t="inlineStr">
+      <c r="H224" s="2" t="inlineStr">
         <is>
           <t>同济大学经济与管理学院应用经济博士后招聘</t>
         </is>
@@ -13202,7 +13192,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K224" s="3" t="inlineStr">
+      <c r="K224" s="2" t="inlineStr">
         <is>
           <t>https://zp.tongji.edu.cn/info/1063/19717.htm</t>
         </is>
@@ -13244,7 +13234,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H225" s="3" t="inlineStr">
+      <c r="H225" s="2" t="inlineStr">
         <is>
           <t>清华大学深圳国际研究生院2026年海外优青（含金融科技/数字智能经济）</t>
         </is>
@@ -13259,7 +13249,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K225" s="3" t="inlineStr">
+      <c r="K225" s="2" t="inlineStr">
         <is>
           <t>https://www.gxszw.com/region/guangdong/gxzpgd/202602/09123430.html</t>
         </is>
@@ -13306,7 +13296,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H226" s="3" t="inlineStr">
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t>清华大学深圳国际研究生院尤海峰课题组2026年招收博士后</t>
         </is>
@@ -13321,7 +13311,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K226" s="3" t="inlineStr">
+      <c r="K226" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/393833.html</t>
         </is>
@@ -13358,7 +13348,7 @@
           <t>经济管理学院</t>
         </is>
       </c>
-      <c r="F227" s="2" t="n">
+      <c r="F227" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G227" t="inlineStr">
@@ -13366,7 +13356,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H227" s="3" t="inlineStr">
+      <c r="H227" s="2" t="inlineStr">
         <is>
           <t>清华大学经济管理学院2026年招聘教研系列教师（经济系）</t>
         </is>
@@ -13381,7 +13371,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K227" s="3" t="inlineStr">
+      <c r="K227" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/381907.html</t>
         </is>
@@ -13418,7 +13408,7 @@
           <t>经济管理学院</t>
         </is>
       </c>
-      <c r="F228" s="2" t="n">
+      <c r="F228" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G228" t="inlineStr">
@@ -13426,7 +13416,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H228" s="3" t="inlineStr">
+      <c r="H228" s="2" t="inlineStr">
         <is>
           <t>清华大学经济管理学院应用经济学流动站（合作导师董丰）2026年招聘博士后</t>
         </is>
@@ -13441,7 +13431,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K228" s="3" t="inlineStr">
+      <c r="K228" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/395746.html</t>
         </is>
@@ -13489,7 +13479,7 @@
         </is>
       </c>
       <c r="G229" t="inlineStr"/>
-      <c r="H229" s="3" t="inlineStr">
+      <c r="H229" s="2" t="inlineStr">
         <is>
           <t>清华大学经济管理学院博士后招聘</t>
         </is>
@@ -13504,7 +13494,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K229" s="3" t="inlineStr">
+      <c r="K229" s="2" t="inlineStr">
         <is>
           <t>https://sem.tsinghua.edu.cn/js/bshldz/bshzp.htm</t>
         </is>
@@ -13551,7 +13541,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H230" s="3" t="inlineStr">
+      <c r="H230" s="2" t="inlineStr">
         <is>
           <t>清华大学经济管理学院教师招聘（2026年10月更新）</t>
         </is>
@@ -13566,7 +13556,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K230" s="3" t="inlineStr">
+      <c r="K230" s="2" t="inlineStr">
         <is>
           <t>https://www.sem.tsinghua.edu.cn/js/jszp.htm</t>
         </is>
@@ -13605,25 +13595,22 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>全球创新与治理研究院</t>
-        </is>
-      </c>
-      <c r="F231" s="2" t="n">
-        <v>45646</v>
+          <t>中国金融学院</t>
+        </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="H231" s="3" t="inlineStr">
-        <is>
-          <t>对外经济贸易大学全球创新与治理研究院2025年专职教学科研人员招聘公告</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>中国金融学院2026年专职教师招聘公告</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>产业经济学方向</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -13631,9 +13618,9 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K231" s="3" t="inlineStr">
-        <is>
-          <t>https://agig.uibe.edu.cn/tzgg/e30c29f3c079417eadaaedb5f16dfc54.htm</t>
+      <c r="K231" s="2" t="inlineStr">
+        <is>
+          <t>https://sbf.uibe.edu.cn/tzgg/b20abafc23f940349876baa87054aace.htm</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -13665,40 +13652,37 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>中国金融学院</t>
-        </is>
-      </c>
-      <c r="F232" s="2" t="n">
-        <v>45992</v>
+          <t>国际经济贸易学院</t>
+        </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H232" s="3" t="inlineStr">
-        <is>
-          <t>中国金融学院2026年专职教师招聘公告</t>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>对外经济贸易大学2026年度事业编专职教学科研人员、师资博士后招聘公告</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>含国际经济贸易学院等经管岗位</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Dept/HR</t>
-        </is>
-      </c>
-      <c r="K232" s="3" t="inlineStr">
-        <is>
-          <t>https://sbf.uibe.edu.cn/tzgg/b20abafc23f940349876baa87054aace.htm</t>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="K232" s="2" t="inlineStr">
+        <is>
+          <t>https://hr.uibe.edu.cn/jszp/zpxx/654c850954d7459abbde78b5ebc62820.htm</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -13725,25 +13709,18 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>国际经济贸易学院</t>
-        </is>
-      </c>
-      <c r="F233" s="2" t="n">
-        <v>45992</v>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H233" s="3" t="inlineStr">
-        <is>
-          <t>对外经济贸易大学2026年度事业编专职教学科研人员、师资博士后招聘公告</t>
+          <t>国际经济贸易学院/中国金融学院/经济学院</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>对外经济贸易大学全球价值链研究院专职教学科研人员招聘相关公告</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>含国际经济贸易学院等经管岗位</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -13751,14 +13728,14 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="K233" s="3" t="inlineStr">
-        <is>
-          <t>https://hr.uibe.edu.cn/jszp/zpxx/654c850954d7459abbde78b5ebc62820.htm</t>
+      <c r="K233" s="2" t="inlineStr">
+        <is>
+          <t>https://hr.uibe.edu.cn/jszp/zpxx/ed338932d6d94149945898e2ab2429c7.htm</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -13785,31 +13762,32 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>国际经济贸易学院/中国金融学院/经济学院</t>
-        </is>
-      </c>
-      <c r="F234" s="2" t="n">
-        <v>46202</v>
-      </c>
-      <c r="G234" t="inlineStr"/>
-      <c r="H234" s="3" t="inlineStr">
-        <is>
-          <t>对外经济贸易大学全球价值链研究院专职教学科研人员招聘相关公告</t>
+          <t>全球创新与治理研究院</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>对外经济贸易大学全球创新与治理研究院2025年专职教学科研人员招聘公告</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>产业经济学方向</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="K234" s="3" t="inlineStr">
-        <is>
-          <t>https://hr.uibe.edu.cn/jszp/zpxx/ed338932d6d94149945898e2ab2429c7.htm</t>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="K234" s="2" t="inlineStr">
+        <is>
+          <t>https://agig.uibe.edu.cn/tzgg/e30c29f3c079417eadaaedb5f16dfc54.htm</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -13845,7 +13823,7 @@
         </is>
       </c>
       <c r="G235" t="inlineStr"/>
-      <c r="H235" s="3" t="inlineStr">
+      <c r="H235" s="2" t="inlineStr">
         <is>
           <t>北京科技大学经济管理学院博士后招聘</t>
         </is>
@@ -13860,7 +13838,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K235" s="3" t="inlineStr">
+      <c r="K235" s="2" t="inlineStr">
         <is>
           <t>https://sem.ustb.edu.cn/szll/bshldz/bshzp/index.htm</t>
         </is>
@@ -13912,7 +13890,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H236" s="3" t="inlineStr">
+      <c r="H236" s="2" t="inlineStr">
         <is>
           <t>经济管理学院2025年诚聘海内外英才</t>
         </is>
@@ -13927,7 +13905,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K236" s="3" t="inlineStr">
+      <c r="K236" s="2" t="inlineStr">
         <is>
           <t>https://sem.ustb.edu.cn/xwzx/tzgg/a2ffc3d9c3d9495baeba6c87e507644c.htm</t>
         </is>
@@ -13979,7 +13957,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H237" s="3" t="inlineStr">
+      <c r="H237" s="2" t="inlineStr">
         <is>
           <t>经济管理学院2025年诚聘海内外英才（人才招聘栏目）</t>
         </is>
@@ -13994,7 +13972,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K237" s="3" t="inlineStr">
+      <c r="K237" s="2" t="inlineStr">
         <is>
           <t>https://sem.ustb.edu.cn/rczp/a2ffc3d9c3d9495baeba6c87e507644c.htm</t>
         </is>
@@ -14042,7 +14020,7 @@
         </is>
       </c>
       <c r="G238" t="inlineStr"/>
-      <c r="H238" s="3" t="inlineStr">
+      <c r="H238" s="2" t="inlineStr">
         <is>
           <t>经济管理学院诚聘海内外英才（师资队伍招聘页）</t>
         </is>
@@ -14057,7 +14035,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K238" s="3" t="inlineStr">
+      <c r="K238" s="2" t="inlineStr">
         <is>
           <t>https://sem.ustb.edu.cn/szll/jszp/index.htm</t>
         </is>
@@ -14100,7 +14078,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H239" s="3" t="inlineStr">
+      <c r="H239" s="2" t="inlineStr">
         <is>
           <t>2026-2027 Wenzhou-Kean University Recruitment for Faculty</t>
         </is>
@@ -14115,7 +14093,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K239" s="3" t="inlineStr">
+      <c r="K239" s="2" t="inlineStr">
         <is>
           <t>https://www.wku.edu.cn/zh-hans/node/5597</t>
         </is>
@@ -14149,7 +14127,7 @@
         </is>
       </c>
       <c r="G240" t="inlineStr"/>
-      <c r="H240" s="3" t="inlineStr">
+      <c r="H240" s="2" t="inlineStr">
         <is>
           <t>Academic positions | Wenzhou-Kean University</t>
         </is>
@@ -14164,7 +14142,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K240" s="3" t="inlineStr">
+      <c r="K240" s="2" t="inlineStr">
         <is>
           <t>https://www.wku.edu.cn/zh-hans/xueshugangwei</t>
         </is>
@@ -14202,7 +14180,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H241" s="3" t="inlineStr">
+      <c r="H241" s="2" t="inlineStr">
         <is>
           <t>温州肯恩大学中美人文与经济研究院2026年高层次人才</t>
         </is>
@@ -14217,7 +14195,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K241" s="3" t="inlineStr">
+      <c r="K241" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/348660.html</t>
         </is>
@@ -14255,7 +14233,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H242" s="3" t="inlineStr">
+      <c r="H242" s="2" t="inlineStr">
         <is>
           <t>温州肯恩大学中美人文与经济研究院2026年高层次人才招聘公告</t>
         </is>
@@ -14270,7 +14248,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K242" s="3" t="inlineStr">
+      <c r="K242" s="2" t="inlineStr">
         <is>
           <t>https://talent.sciencenet.cn/index.php?s=Info%2Findex%2Fid%2F24766</t>
         </is>
@@ -14307,12 +14285,15 @@
           <t>嘉庚学院会计与金融学院</t>
         </is>
       </c>
+      <c r="F243" s="3" t="n">
+        <v>46310</v>
+      </c>
       <c r="G243" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H243" s="3" t="inlineStr">
+      <c r="H243" s="2" t="inlineStr">
         <is>
           <t>会计与金融学院2026—2027学年专任教师招聘启事</t>
         </is>
@@ -14327,7 +14308,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K243" s="3" t="inlineStr">
+      <c r="K243" s="2" t="inlineStr">
         <is>
           <t>https://hr.xujc.com/zhaopin/teacher/215.html</t>
         </is>
@@ -14346,7 +14327,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>??</t>
+          <t>厦门</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -14361,17 +14342,20 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>?????/????????</t>
-        </is>
+          <t>经济学院/WISE</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="n">
+        <v>46356</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H244" s="3" t="inlineStr">
-        <is>
-          <t>厦门大学2026年博士后招收启事</t>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>厦门大学WISE/经济学院2026-2027年诚聘海外研究人员（英才网）</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -14384,14 +14368,14 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K244" s="3" t="inlineStr">
-        <is>
-          <t>https://postdoctor.xmu.edu.cn/info/1061/4196.htm</t>
+      <c r="K244" s="2" t="inlineStr">
+        <is>
+          <t>http://www.gaoxiaozp.com/fujian/62361.html</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -14403,7 +14387,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>厦门</t>
+          <t>??</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -14418,7 +14402,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>经济学院/WISE</t>
+          <t>?????/????????</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -14426,9 +14410,9 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H245" s="3" t="inlineStr">
-        <is>
-          <t>厦门大学WISE/经济学院2026-2027年诚聘海外研究人员（英才网）</t>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>厦门大学2026年博士后招收启事</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -14441,14 +14425,14 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K245" s="3" t="inlineStr">
-        <is>
-          <t>http://www.gaoxiaozp.com/fujian/62361.html</t>
+      <c r="K245" s="2" t="inlineStr">
+        <is>
+          <t>https://postdoctor.xmu.edu.cn/info/1061/4196.htm</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14467,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H246" s="3" t="inlineStr">
+      <c r="H246" s="2" t="inlineStr">
         <is>
           <t>厦门大学王亚南经济研究院2025年诚邀海内外英才</t>
         </is>
@@ -14498,7 +14482,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K246" s="3" t="inlineStr">
+      <c r="K246" s="2" t="inlineStr">
         <is>
           <t>https://www.gxszw.com/region/fujian/gxzpfj/202508/19118908.html</t>
         </is>
@@ -14536,7 +14520,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H247" s="3" t="inlineStr">
+      <c r="H247" s="2" t="inlineStr">
         <is>
           <t>燕山大学2026年公开选聘专任教师公告</t>
         </is>
@@ -14551,7 +14535,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K247" s="3" t="inlineStr">
+      <c r="K247" s="2" t="inlineStr">
         <is>
           <t>http://jrzhufu.com/zhaopin/article/2269.html</t>
         </is>
@@ -14585,7 +14569,7 @@
         </is>
       </c>
       <c r="G248" t="inlineStr"/>
-      <c r="H248" s="3" t="inlineStr">
+      <c r="H248" s="2" t="inlineStr">
         <is>
           <t>燕山大学经济学专任教师招聘</t>
         </is>
@@ -14600,7 +14584,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K248" s="3" t="inlineStr">
+      <c r="K248" s="2" t="inlineStr">
         <is>
           <t>https://www.sciencehr.net/job/229026.html</t>
         </is>
@@ -14633,7 +14617,7 @@
           <t>人事处</t>
         </is>
       </c>
-      <c r="F249" s="2" t="n">
+      <c r="F249" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G249" t="inlineStr">
@@ -14641,7 +14625,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H249" s="3" t="inlineStr">
+      <c r="H249" s="2" t="inlineStr">
         <is>
           <t>浙江工商大学2026年招收博士后公告（gaoxiaojob）</t>
         </is>
@@ -14656,7 +14640,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K249" s="3" t="inlineStr">
+      <c r="K249" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/391400.html</t>
         </is>
@@ -14689,7 +14673,7 @@
           <t>人事处</t>
         </is>
       </c>
-      <c r="F250" s="2" t="n">
+      <c r="F250" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G250" t="inlineStr">
@@ -14697,7 +14681,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H250" s="3" t="inlineStr">
+      <c r="H250" s="2" t="inlineStr">
         <is>
           <t>浙江工商大学2026年特殊专业技术岗位</t>
         </is>
@@ -14712,7 +14696,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K250" s="3" t="inlineStr">
+      <c r="K250" s="2" t="inlineStr">
         <is>
           <t>https://m.gaoxiaojob.com/announcement/detail/384690.html</t>
         </is>
@@ -14750,7 +14734,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H251" s="3" t="inlineStr">
+      <c r="H251" s="2" t="inlineStr">
         <is>
           <t>浙江工商大学2026年公开招聘专任教师等公告</t>
         </is>
@@ -14765,7 +14749,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K251" s="3" t="inlineStr">
+      <c r="K251" s="2" t="inlineStr">
         <is>
           <t>http://jrrc.jrzp.com/gaoxiao/zpview_6CAE97FB21CFD1BA.shtml</t>
         </is>
@@ -14803,7 +14787,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H252" s="3" t="inlineStr">
+      <c r="H252" s="2" t="inlineStr">
         <is>
           <t>浙江工商大学2026年博士后招收公告</t>
         </is>
@@ -14818,7 +14802,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K252" s="3" t="inlineStr">
+      <c r="K252" s="2" t="inlineStr">
         <is>
           <t>http://hr.zjgsu.edu.cn/View-1791.html</t>
         </is>
@@ -14856,7 +14840,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H253" s="3" t="inlineStr">
+      <c r="H253" s="2" t="inlineStr">
         <is>
           <t>浙江工商大学统计与数学学院2025诚聘英才</t>
         </is>
@@ -14871,7 +14855,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K253" s="3" t="inlineStr">
+      <c r="K253" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/321984.html</t>
         </is>
@@ -14904,7 +14888,7 @@
           <t>经济学院</t>
         </is>
       </c>
-      <c r="F254" s="2" t="n">
+      <c r="F254" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G254" t="inlineStr">
@@ -14912,7 +14896,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H254" s="3" t="inlineStr">
+      <c r="H254" s="2" t="inlineStr">
         <is>
           <t>浙江工业大学2026年特殊专业技术岗位招聘</t>
         </is>
@@ -14927,7 +14911,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K254" s="3" t="inlineStr">
+      <c r="K254" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/384652.html</t>
         </is>
@@ -14965,7 +14949,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H255" s="3" t="inlineStr">
+      <c r="H255" s="2" t="inlineStr">
         <is>
           <t>浙江工业大学2025年高层次人才招聘公告</t>
         </is>
@@ -14980,7 +14964,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K255" s="3" t="inlineStr">
+      <c r="K255" s="2" t="inlineStr">
         <is>
           <t>http://www.rczp.zjut.edu.cn/2025/0313/c5346a300033/page.htm</t>
         </is>
@@ -15018,7 +15002,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H256" s="3" t="inlineStr">
+      <c r="H256" s="2" t="inlineStr">
         <is>
           <t>浙江工业大学2026年高层次人才招聘公告</t>
         </is>
@@ -15033,7 +15017,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K256" s="3" t="inlineStr">
+      <c r="K256" s="2" t="inlineStr">
         <is>
           <t>http://www.rczp.zjut.edu.cn/2026/0312/c5346a328902/page.htm</t>
         </is>
@@ -15066,17 +15050,17 @@
           <t>经济管理学院</t>
         </is>
       </c>
-      <c r="F257" s="2" t="n">
-        <v>46387</v>
+      <c r="F257" s="3" t="n">
+        <v>46344</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H257" s="3" t="inlineStr">
-        <is>
-          <t>浙江理工大学2026年特殊专业技术岗位招聘</t>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>浙江理工大学2026年人才招聘公告</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -15089,14 +15073,14 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K257" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gaoxiaojob.com/announcement/detail/432389.html</t>
+      <c r="K257" s="2" t="inlineStr">
+        <is>
+          <t>https://news.zstu.edu.cn/info/1113/51843.htm</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -15122,14 +15106,17 @@
           <t>经济管理学院</t>
         </is>
       </c>
+      <c r="F258" s="3" t="n">
+        <v>46387</v>
+      </c>
       <c r="G258" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H258" s="3" t="inlineStr">
-        <is>
-          <t>浙江理工大学2026年人才招聘公告</t>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>浙江理工大学2026年特殊专业技术岗位招聘</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -15142,14 +15129,14 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K258" s="3" t="inlineStr">
-        <is>
-          <t>https://news.zstu.edu.cn/info/1113/51843.htm</t>
+      <c r="K258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gaoxiaojob.com/announcement/detail/432389.html</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -15175,7 +15162,7 @@
           <t>人事处</t>
         </is>
       </c>
-      <c r="F259" s="2" t="n">
+      <c r="F259" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G259" t="inlineStr">
@@ -15183,7 +15170,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H259" s="3" t="inlineStr">
+      <c r="H259" s="2" t="inlineStr">
         <is>
           <t>浙江财经大学2026年特殊专业技术岗位</t>
         </is>
@@ -15198,7 +15185,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K259" s="3" t="inlineStr">
+      <c r="K259" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/432519.html</t>
         </is>
@@ -15236,7 +15223,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H260" s="3" t="inlineStr">
+      <c r="H260" s="2" t="inlineStr">
         <is>
           <t>浙江财经大学2026年人才引进公告</t>
         </is>
@@ -15251,7 +15238,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K260" s="3" t="inlineStr">
+      <c r="K260" s="2" t="inlineStr">
         <is>
           <t>https://rsc.zufe.edu.cn/info/1073/3604.htm</t>
         </is>
@@ -15289,7 +15276,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H261" s="3" t="inlineStr">
+      <c r="H261" s="2" t="inlineStr">
         <is>
           <t>浙江财经大学2026年博士后招聘公告</t>
         </is>
@@ -15304,7 +15291,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K261" s="3" t="inlineStr">
+      <c r="K261" s="2" t="inlineStr">
         <is>
           <t>https://rsc.zufe.edu.cn/info/1073/3738.htm</t>
         </is>
@@ -15342,7 +15329,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H262" s="3" t="inlineStr">
+      <c r="H262" s="2" t="inlineStr">
         <is>
           <t>浙江财经大学科技金融重点实验室2026年专职研究员</t>
         </is>
@@ -15357,7 +15344,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K262" s="3" t="inlineStr">
+      <c r="K262" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/407749.html</t>
         </is>
@@ -15395,7 +15382,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H263" s="3" t="inlineStr">
+      <c r="H263" s="2" t="inlineStr">
         <is>
           <t>浙江财经大学高等研究院2026年人才引进公告</t>
         </is>
@@ -15410,7 +15397,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K263" s="3" t="inlineStr">
+      <c r="K263" s="2" t="inlineStr">
         <is>
           <t>https://rsc.zufe.edu.cn/info/1073/3709.htm</t>
         </is>
@@ -15447,15 +15434,15 @@
           <t>国际联合商学院</t>
         </is>
       </c>
-      <c r="F264" s="2" t="n">
-        <v>46305</v>
+      <c r="F264" s="3" t="n">
+        <v>46326</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H264" s="3" t="inlineStr">
+      <c r="H264" s="2" t="inlineStr">
         <is>
           <t>2026年浙江大学“求是博士后”全球招募公告</t>
         </is>
@@ -15470,7 +15457,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K264" s="3" t="inlineStr">
+      <c r="K264" s="2" t="inlineStr">
         <is>
           <t>https://zibs.zju.edu.cn/2026/0417/c82074a3153130/page.htm</t>
         </is>
@@ -15507,7 +15494,7 @@
           <t>管理学院</t>
         </is>
       </c>
-      <c r="F265" s="2" t="n">
+      <c r="F265" s="3" t="n">
         <v>46508</v>
       </c>
       <c r="G265" t="inlineStr">
@@ -15515,7 +15502,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H265" s="3" t="inlineStr">
+      <c r="H265" s="2" t="inlineStr">
         <is>
           <t>浙江大学管理学院2026年招聘学科博士后</t>
         </is>
@@ -15530,7 +15517,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K265" s="3" t="inlineStr">
+      <c r="K265" s="2" t="inlineStr">
         <is>
           <t>https://m.gaoxiaojob.com/announcement/detail/400624.html</t>
         </is>
@@ -15572,7 +15559,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H266" s="3" t="inlineStr">
+      <c r="H266" s="2" t="inlineStr">
         <is>
           <t>浙江大学ZIBS2026年博士后招聘</t>
         </is>
@@ -15587,7 +15574,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K266" s="3" t="inlineStr">
+      <c r="K266" s="2" t="inlineStr">
         <is>
           <t>https://m.gaoxiaojob.com/announcement/detail/368647.html</t>
         </is>
@@ -15625,7 +15612,7 @@
         </is>
       </c>
       <c r="G267" t="inlineStr"/>
-      <c r="H267" s="3" t="inlineStr">
+      <c r="H267" s="2" t="inlineStr">
         <is>
           <t>浙江大学ZIBS博士后研究人员招聘</t>
         </is>
@@ -15640,7 +15627,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K267" s="3" t="inlineStr">
+      <c r="K267" s="2" t="inlineStr">
         <is>
           <t>https://www.gaoxiaojob.com/announcement/detail/19061.html</t>
         </is>
@@ -15678,7 +15665,7 @@
         </is>
       </c>
       <c r="G268" t="inlineStr"/>
-      <c r="H268" s="3" t="inlineStr">
+      <c r="H268" s="2" t="inlineStr">
         <is>
           <t>浙江大学国际校区海纳人才全球招聘</t>
         </is>
@@ -15693,7 +15680,7 @@
           <t>Dept/HR</t>
         </is>
       </c>
-      <c r="K268" s="3" t="inlineStr">
+      <c r="K268" s="2" t="inlineStr">
         <is>
           <t>https://www.intl.zju.edu.cn/zh-hans/recruit/16747</t>
         </is>
@@ -15727,7 +15714,7 @@
         </is>
       </c>
       <c r="G269" t="inlineStr"/>
-      <c r="H269" s="3" t="inlineStr">
+      <c r="H269" s="2" t="inlineStr">
         <is>
           <t>Professor/Associate/Assistant — Economics (IUSD)</t>
         </is>
@@ -15742,7 +15729,7 @@
           <t>CityU-Career</t>
         </is>
       </c>
-      <c r="K269" s="3" t="inlineStr">
+      <c r="K269" s="2" t="inlineStr">
         <is>
           <t>https://career.cityu.edu.mo</t>
         </is>
@@ -15781,7 +15768,7 @@
         </is>
       </c>
       <c r="G270" t="inlineStr"/>
-      <c r="H270" s="3" t="inlineStr">
+      <c r="H270" s="2" t="inlineStr">
         <is>
           <t>Faculty (Economics among areas) — School of Business</t>
         </is>
@@ -15796,7 +15783,7 @@
           <t>MUST-Career</t>
         </is>
       </c>
-      <c r="K270" s="3" t="inlineStr">
+      <c r="K270" s="2" t="inlineStr">
         <is>
           <t>https://www.must.edu.mo/en/careers</t>
         </is>
@@ -15839,7 +15826,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H271" s="3" t="inlineStr">
+      <c r="H271" s="2" t="inlineStr">
         <is>
           <t>Assistant Professor in Economics (macro/monetary)</t>
         </is>
@@ -15854,7 +15841,7 @@
           <t>UM-Career</t>
         </is>
       </c>
-      <c r="K271" s="3" t="inlineStr">
+      <c r="K271" s="2" t="inlineStr">
         <is>
           <t>https://career.admo.um.edu.mo/fss_deco_ap_04_2026/</t>
         </is>
@@ -15897,7 +15884,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H272" s="3" t="inlineStr">
+      <c r="H272" s="2" t="inlineStr">
         <is>
           <t>Assistant Professor in Tourism Economics</t>
         </is>
@@ -15912,7 +15899,7 @@
           <t>UM-Career</t>
         </is>
       </c>
-      <c r="K272" s="3" t="inlineStr">
+      <c r="K272" s="2" t="inlineStr">
         <is>
           <t>https://career.admo.um.edu.mo/fba_drtm_te_ap_05_2026/</t>
         </is>
@@ -15955,7 +15942,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H273" s="3" t="inlineStr">
+      <c r="H273" s="2" t="inlineStr">
         <is>
           <t>Associate/Assistant Professor in Microeconometrics</t>
         </is>
@@ -15970,7 +15957,7 @@
           <t>UM-Career</t>
         </is>
       </c>
-      <c r="K273" s="3" t="inlineStr">
+      <c r="K273" s="2" t="inlineStr">
         <is>
           <t>https://career.admo.um.edu.mo/fba_fbe_mec_aap_08_2026/</t>
         </is>
@@ -16008,11 +15995,11 @@
           <t>Department of Economics</t>
         </is>
       </c>
-      <c r="F274" s="2" t="n">
+      <c r="F274" s="3" t="n">
         <v>46354</v>
       </c>
       <c r="G274" t="inlineStr"/>
-      <c r="H274" s="3" t="inlineStr">
+      <c r="H274" s="2" t="inlineStr">
         <is>
           <t>Assistant/Associate/Professor (any field)</t>
         </is>
@@ -16027,7 +16014,7 @@
           <t>JOE</t>
         </is>
       </c>
-      <c r="K274" s="3" t="inlineStr">
+      <c r="K274" s="2" t="inlineStr">
         <is>
           <t>https://ann.ncku.edu.tw/p/404-1013-305836.php?Lang=zh-tw</t>
         </is>
@@ -16065,11 +16052,11 @@
           <t>Department of Economics</t>
         </is>
       </c>
-      <c r="F275" s="2" t="n">
+      <c r="F275" s="3" t="n">
         <v>46356</v>
       </c>
       <c r="G275" t="inlineStr"/>
-      <c r="H275" s="3" t="inlineStr">
+      <c r="H275" s="2" t="inlineStr">
         <is>
           <t>Open-rank tenure-track faculty (1)</t>
         </is>
@@ -16084,7 +16071,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K275" s="3" t="inlineStr">
+      <c r="K275" s="2" t="inlineStr">
         <is>
           <t>https://econo.nccu.edu.tw/eng/PageDoc/Detail?fid=1052&amp;id=42260</t>
         </is>
@@ -16126,11 +16113,11 @@
           <t>Department of Political Economy</t>
         </is>
       </c>
-      <c r="F276" s="2" t="n">
+      <c r="F276" s="3" t="n">
         <v>46387</v>
       </c>
       <c r="G276" t="inlineStr"/>
-      <c r="H276" s="3" t="inlineStr">
+      <c r="H276" s="2" t="inlineStr">
         <is>
           <t>Faculty (2) — Political Economy / Economics</t>
         </is>
@@ -16145,7 +16132,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="K276" s="3" t="inlineStr">
+      <c r="K276" s="2" t="inlineStr">
         <is>
           <t>https://www.nstc.gov.tw/folksonomy/detail/4b115db7-4cd9-4774-8ba4-31335f5ea07c?l=en</t>
         </is>
@@ -16183,11 +16170,11 @@
           <t>Department of Economics</t>
         </is>
       </c>
-      <c r="F277" s="2" t="n">
-        <v>46353</v>
+      <c r="F277" s="3" t="n">
+        <v>46418</v>
       </c>
       <c r="G277" t="inlineStr"/>
-      <c r="H277" s="3" t="inlineStr">
+      <c r="H277" s="2" t="inlineStr">
         <is>
           <t>Assistant Professor or above (up to 3)</t>
         </is>
@@ -16202,7 +16189,7 @@
           <t>Dept/JOE</t>
         </is>
       </c>
-      <c r="K277" s="3" t="inlineStr">
+      <c r="K277" s="2" t="inlineStr">
         <is>
           <t>https://econ.ntu.edu.tw/archives/18834</t>
         </is>
@@ -16244,11 +16231,11 @@
           <t>Taipei School of Economics and Political Science (TSE)</t>
         </is>
       </c>
-      <c r="F278" s="2" t="n">
+      <c r="F278" s="3" t="n">
         <v>46310</v>
       </c>
       <c r="G278" t="inlineStr"/>
-      <c r="H278" s="3" t="inlineStr">
+      <c r="H278" s="2" t="inlineStr">
         <is>
           <t>Faculty — Macroeconomics / International Trade</t>
         </is>
@@ -16263,7 +16250,7 @@
           <t>JOE</t>
         </is>
       </c>
-      <c r="K278" s="3" t="inlineStr">
+      <c r="K278" s="2" t="inlineStr">
         <is>
           <t>http://www.tse.nthu.edu.tw/post/82-tse-job-opening</t>
         </is>
@@ -16305,11 +16292,11 @@
           <t>Department of Economics</t>
         </is>
       </c>
-      <c r="F279" s="2" t="n">
+      <c r="F279" s="3" t="n">
         <v>46325</v>
       </c>
       <c r="G279" t="inlineStr"/>
-      <c r="H279" s="3" t="inlineStr">
+      <c r="H279" s="2" t="inlineStr">
         <is>
           <t>Assistant Professor or above (2)</t>
         </is>
@@ -16324,7 +16311,7 @@
           <t>Email/Mail</t>
         </is>
       </c>
-      <c r="K279" s="3" t="inlineStr">
+      <c r="K279" s="2" t="inlineStr">
         <is>
           <t>https://web-ch.scu.edu.tw/econ/opinion/16118/31786</t>
         </is>
